--- a/research/traditional_assets/database/data/peru/peru_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/peru/peru_business_consumer_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1074375326552792</v>
+        <v>0.1071523169339461</v>
       </c>
       <c r="C2">
-        <v>54.79645927167577</v>
+        <v>54.37839721905326</v>
       </c>
       <c r="D2">
-        <v>36.19645927167577</v>
+        <v>36.34139721905326</v>
       </c>
       <c r="E2">
-        <v>-13.3</v>
+        <v>-12.737</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G2">
         <v>18.6</v>
@@ -1439,28 +1439,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0283189</v>
       </c>
       <c r="N2">
-        <v>8.585000000000001</v>
+        <v>8.5566811</v>
       </c>
       <c r="O2">
-        <v>2.532575</v>
+        <v>2.5242209245</v>
       </c>
       <c r="P2">
-        <v>6.052425000000001</v>
+        <v>6.032460175500001</v>
       </c>
       <c r="Q2">
-        <v>13.592425</v>
+        <v>13.5724601755</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1074375326552792</v>
+        <v>0.1078764665999455</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927493</v>
+        <v>0.9603031956190158</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>303.1544304333855</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1071523169339461</v>
+        <v>0.106867101212613</v>
       </c>
       <c r="C3">
-        <v>54.37839721905326</v>
+        <v>53.96150055462066</v>
       </c>
       <c r="D3">
-        <v>36.34139721905326</v>
+        <v>36.48750055462065</v>
       </c>
       <c r="E3">
-        <v>-12.737</v>
+        <v>-12.174</v>
       </c>
       <c r="F3">
-        <v>0.5629999999999999</v>
+        <v>1.126</v>
       </c>
       <c r="G3">
         <v>18.6</v>
@@ -1521,28 +1521,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M3">
-        <v>0.0283189</v>
+        <v>0.0566378</v>
       </c>
       <c r="N3">
-        <v>8.5566811</v>
+        <v>8.5283622</v>
       </c>
       <c r="O3">
-        <v>2.5242209245</v>
+        <v>2.515866849</v>
       </c>
       <c r="P3">
-        <v>6.032460175500001</v>
+        <v>6.012495351</v>
       </c>
       <c r="Q3">
-        <v>13.5724601755</v>
+        <v>13.552495351</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1078764665999455</v>
+        <v>0.1083243583802174</v>
       </c>
       <c r="T3">
-        <v>0.9603031956190158</v>
+        <v>0.9672319390131654</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>303.1544304333855</v>
+        <v>151.5772152166928</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.106867101212613</v>
+        <v>0.1065818854912799</v>
       </c>
       <c r="C4">
-        <v>53.96150055462066</v>
+        <v>53.54578339074592</v>
       </c>
       <c r="D4">
-        <v>36.48750055462065</v>
+        <v>36.63478339074592</v>
       </c>
       <c r="E4">
-        <v>-12.174</v>
+        <v>-11.611</v>
       </c>
       <c r="F4">
-        <v>1.126</v>
+        <v>1.689</v>
       </c>
       <c r="G4">
         <v>18.6</v>
@@ -1603,28 +1603,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M4">
-        <v>0.0566378</v>
+        <v>0.08495669999999998</v>
       </c>
       <c r="N4">
-        <v>8.5283622</v>
+        <v>8.500043300000002</v>
       </c>
       <c r="O4">
-        <v>2.515866849</v>
+        <v>2.5075127735</v>
       </c>
       <c r="P4">
-        <v>6.012495351</v>
+        <v>5.992530526500001</v>
       </c>
       <c r="Q4">
-        <v>13.552495351</v>
+        <v>13.5325305265</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1083243583802174</v>
+        <v>0.1087814850425566</v>
       </c>
       <c r="T4">
-        <v>0.9672319390131654</v>
+        <v>0.9743035430958541</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>151.5772152166928</v>
+        <v>101.0514768111285</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1065818854912799</v>
+        <v>0.1062966697699468</v>
       </c>
       <c r="C5">
-        <v>53.54578339074592</v>
+        <v>53.13126006858042</v>
       </c>
       <c r="D5">
-        <v>36.63478339074592</v>
+        <v>36.78326006858042</v>
       </c>
       <c r="E5">
-        <v>-11.611</v>
+        <v>-11.048</v>
       </c>
       <c r="F5">
-        <v>1.689</v>
+        <v>2.252</v>
       </c>
       <c r="G5">
         <v>18.6</v>
@@ -1685,28 +1685,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M5">
-        <v>0.08495669999999998</v>
+        <v>0.1132756</v>
       </c>
       <c r="N5">
-        <v>8.500043300000002</v>
+        <v>8.471724400000001</v>
       </c>
       <c r="O5">
-        <v>2.5075127735</v>
+        <v>2.499158698</v>
       </c>
       <c r="P5">
-        <v>5.992530526500001</v>
+        <v>5.972565702000001</v>
       </c>
       <c r="Q5">
-        <v>13.5325305265</v>
+        <v>13.512565702</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1087814850425566</v>
+        <v>0.109248135177028</v>
       </c>
       <c r="T5">
-        <v>0.9743035430958541</v>
+        <v>0.9815224722635988</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>101.0514768111285</v>
+        <v>75.78860760834638</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1062966697699468</v>
+        <v>0.1060114540486138</v>
       </c>
       <c r="C6">
-        <v>53.13126006858042</v>
+        <v>52.71794516271387</v>
       </c>
       <c r="D6">
-        <v>36.78326006858042</v>
+        <v>36.93294516271386</v>
       </c>
       <c r="E6">
-        <v>-11.048</v>
+        <v>-10.485</v>
       </c>
       <c r="F6">
-        <v>2.252</v>
+        <v>2.815</v>
       </c>
       <c r="G6">
         <v>18.6</v>
@@ -1767,28 +1767,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M6">
-        <v>0.1132756</v>
+        <v>0.1415945</v>
       </c>
       <c r="N6">
-        <v>8.471724400000001</v>
+        <v>8.443405500000001</v>
       </c>
       <c r="O6">
-        <v>2.499158698</v>
+        <v>2.4908046225</v>
       </c>
       <c r="P6">
-        <v>5.972565702000001</v>
+        <v>5.9526008775</v>
       </c>
       <c r="Q6">
-        <v>13.512565702</v>
+        <v>13.4926008775</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.109248135177028</v>
+        <v>0.1097246095248566</v>
       </c>
       <c r="T6">
-        <v>0.9815224722635988</v>
+        <v>0.9888933788875066</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.78860760834638</v>
+        <v>60.63088608667711</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1060114540486138</v>
+        <v>0.1057262383272807</v>
       </c>
       <c r="C7">
-        <v>52.71794516271387</v>
+        <v>52.30585348594368</v>
       </c>
       <c r="D7">
-        <v>36.93294516271386</v>
+        <v>37.08385348594368</v>
       </c>
       <c r="E7">
-        <v>-10.485</v>
+        <v>-9.922000000000001</v>
       </c>
       <c r="F7">
-        <v>2.815</v>
+        <v>3.378</v>
       </c>
       <c r="G7">
         <v>18.6</v>
@@ -1849,28 +1849,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M7">
-        <v>0.1415945</v>
+        <v>0.1699134</v>
       </c>
       <c r="N7">
-        <v>8.443405500000001</v>
+        <v>8.4150866</v>
       </c>
       <c r="O7">
-        <v>2.4908046225</v>
+        <v>2.482450547</v>
       </c>
       <c r="P7">
-        <v>5.9526008775</v>
+        <v>5.932636053</v>
       </c>
       <c r="Q7">
-        <v>13.4926008775</v>
+        <v>13.472636053</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1097246095248566</v>
+        <v>0.1102112216247667</v>
       </c>
       <c r="T7">
-        <v>0.9888933788875066</v>
+        <v>0.996421113311923</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.63088608667711</v>
+        <v>50.52573840556425</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1057262383272807</v>
+        <v>0.1054410226059476</v>
       </c>
       <c r="C8">
-        <v>52.30585348594368</v>
+        <v>51.8950000941613</v>
       </c>
       <c r="D8">
-        <v>37.08385348594368</v>
+        <v>37.23600009416131</v>
       </c>
       <c r="E8">
-        <v>-9.922000000000001</v>
+        <v>-9.359000000000002</v>
       </c>
       <c r="F8">
-        <v>3.378</v>
+        <v>3.940999999999999</v>
       </c>
       <c r="G8">
         <v>18.6</v>
@@ -1931,28 +1931,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M8">
-        <v>0.1699134</v>
+        <v>0.1982323</v>
       </c>
       <c r="N8">
-        <v>8.4150866</v>
+        <v>8.3867677</v>
       </c>
       <c r="O8">
-        <v>2.482450547</v>
+        <v>2.4740964715</v>
       </c>
       <c r="P8">
-        <v>5.932636053</v>
+        <v>5.912671228500001</v>
       </c>
       <c r="Q8">
-        <v>13.472636053</v>
+        <v>13.4526712285</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1102112216247667</v>
+        <v>0.110708298501019</v>
       </c>
       <c r="T8">
-        <v>0.996421113311923</v>
+        <v>1.004110734498155</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.52573840556426</v>
+        <v>43.30777577619793</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1054410226059476</v>
+        <v>0.1051558068846146</v>
       </c>
       <c r="C9">
-        <v>51.8950000941613</v>
+        <v>51.48540029135972</v>
       </c>
       <c r="D9">
-        <v>37.23600009416131</v>
+        <v>37.38940029135971</v>
       </c>
       <c r="E9">
-        <v>-9.359</v>
+        <v>-8.796000000000001</v>
       </c>
       <c r="F9">
-        <v>3.941</v>
+        <v>4.504</v>
       </c>
       <c r="G9">
         <v>18.6</v>
@@ -2013,28 +2013,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M9">
-        <v>0.1982323</v>
+        <v>0.2265512</v>
       </c>
       <c r="N9">
-        <v>8.3867677</v>
+        <v>8.358448800000001</v>
       </c>
       <c r="O9">
-        <v>2.4740964715</v>
+        <v>2.465742396</v>
       </c>
       <c r="P9">
-        <v>5.912671228500001</v>
+        <v>5.892706404000001</v>
       </c>
       <c r="Q9">
-        <v>13.4526712285</v>
+        <v>13.432706404</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.110708298501019</v>
+        <v>0.1112161813963202</v>
       </c>
       <c r="T9">
-        <v>1.004110734498155</v>
+        <v>1.011967521362348</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.30777577619793</v>
+        <v>37.89430380417319</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1051558068846146</v>
+        <v>0.1048705911632815</v>
       </c>
       <c r="C10">
-        <v>51.48540029135972</v>
+        <v>51.07706963476505</v>
       </c>
       <c r="D10">
-        <v>37.38940029135971</v>
+        <v>37.54406963476505</v>
       </c>
       <c r="E10">
-        <v>-8.796000000000001</v>
+        <v>-8.233000000000001</v>
       </c>
       <c r="F10">
-        <v>4.504</v>
+        <v>5.066999999999999</v>
       </c>
       <c r="G10">
         <v>18.6</v>
@@ -2095,28 +2095,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M10">
-        <v>0.2265512</v>
+        <v>0.2548700999999999</v>
       </c>
       <c r="N10">
-        <v>8.358448800000001</v>
+        <v>8.330129900000001</v>
       </c>
       <c r="O10">
-        <v>2.465742396</v>
+        <v>2.4573883205</v>
       </c>
       <c r="P10">
-        <v>5.892706404000001</v>
+        <v>5.872741579500001</v>
       </c>
       <c r="Q10">
-        <v>13.432706404</v>
+        <v>13.4127415795</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1112161813963202</v>
+        <v>0.1117352265530566</v>
       </c>
       <c r="T10">
-        <v>1.011967521362348</v>
+        <v>1.01999698486092</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.89430380417319</v>
+        <v>33.68382560370951</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1048705911632815</v>
+        <v>0.1045853754419484</v>
       </c>
       <c r="C11">
-        <v>51.07706963476505</v>
+        <v>50.67002394009599</v>
       </c>
       <c r="D11">
-        <v>37.54406963476505</v>
+        <v>37.70002394009599</v>
       </c>
       <c r="E11">
-        <v>-8.233000000000001</v>
+        <v>-7.670000000000002</v>
       </c>
       <c r="F11">
-        <v>5.066999999999999</v>
+        <v>5.629999999999999</v>
       </c>
       <c r="G11">
         <v>18.6</v>
@@ -2177,28 +2177,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M11">
-        <v>0.2548700999999999</v>
+        <v>0.2831889999999999</v>
       </c>
       <c r="N11">
-        <v>8.330129900000001</v>
+        <v>8.301811000000001</v>
       </c>
       <c r="O11">
-        <v>2.4573883205</v>
+        <v>2.449034245</v>
       </c>
       <c r="P11">
-        <v>5.872741579500001</v>
+        <v>5.852776755000001</v>
       </c>
       <c r="Q11">
-        <v>13.4127415795</v>
+        <v>13.392776755</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1117352265530566</v>
+        <v>0.1122658060466094</v>
       </c>
       <c r="T11">
-        <v>1.01999698486092</v>
+        <v>1.028204880881681</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.68382560370951</v>
+        <v>30.31544304333856</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1045853754419484</v>
+        <v>0.1043001597206153</v>
       </c>
       <c r="C12">
-        <v>50.67002394009599</v>
+        <v>50.26427928695509</v>
       </c>
       <c r="D12">
-        <v>37.70002394009599</v>
+        <v>37.85727928695509</v>
       </c>
       <c r="E12">
-        <v>-7.670000000000001</v>
+        <v>-7.107000000000001</v>
       </c>
       <c r="F12">
-        <v>5.63</v>
+        <v>6.193</v>
       </c>
       <c r="G12">
         <v>18.6</v>
@@ -2259,28 +2259,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M12">
-        <v>0.283189</v>
+        <v>0.3115078999999999</v>
       </c>
       <c r="N12">
-        <v>8.301811000000001</v>
+        <v>8.2734921</v>
       </c>
       <c r="O12">
-        <v>2.449034245</v>
+        <v>2.4406801695</v>
       </c>
       <c r="P12">
-        <v>5.852776755000001</v>
+        <v>5.8328119305</v>
       </c>
       <c r="Q12">
-        <v>13.392776755</v>
+        <v>13.3728119305</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1122658060466094</v>
+        <v>0.1128083086748487</v>
       </c>
       <c r="T12">
-        <v>1.028204880881681</v>
+        <v>1.036597224004033</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.31544304333855</v>
+        <v>27.55949367576232</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1043001597206153</v>
+        <v>0.1040149439992823</v>
       </c>
       <c r="C13">
-        <v>50.26427928695509</v>
+        <v>49.85985202435528</v>
       </c>
       <c r="D13">
-        <v>37.85727928695509</v>
+        <v>38.01585202435528</v>
       </c>
       <c r="E13">
-        <v>-7.107000000000001</v>
+        <v>-6.544000000000001</v>
       </c>
       <c r="F13">
-        <v>6.193</v>
+        <v>6.755999999999999</v>
       </c>
       <c r="G13">
         <v>18.6</v>
@@ -2341,28 +2341,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M13">
-        <v>0.3115078999999999</v>
+        <v>0.3398267999999999</v>
       </c>
       <c r="N13">
-        <v>8.2734921</v>
+        <v>8.245173200000002</v>
       </c>
       <c r="O13">
-        <v>2.4406801695</v>
+        <v>2.432326094</v>
       </c>
       <c r="P13">
-        <v>5.8328119305</v>
+        <v>5.812847106000001</v>
       </c>
       <c r="Q13">
-        <v>13.3728119305</v>
+        <v>13.352847106</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1128083086748487</v>
+        <v>0.1133631409082753</v>
       </c>
       <c r="T13">
-        <v>1.036597224004033</v>
+        <v>1.045180302197348</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.55949367576232</v>
+        <v>25.26286920278213</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1040149439992823</v>
+        <v>0.1037297282779492</v>
       </c>
       <c r="C14">
-        <v>49.85985202435528</v>
+        <v>49.4567587763861</v>
       </c>
       <c r="D14">
-        <v>38.01585202435528</v>
+        <v>38.1757587763861</v>
       </c>
       <c r="E14">
-        <v>-6.544000000000001</v>
+        <v>-5.981000000000001</v>
       </c>
       <c r="F14">
-        <v>6.755999999999999</v>
+        <v>7.319</v>
       </c>
       <c r="G14">
         <v>18.6</v>
@@ -2423,28 +2423,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M14">
-        <v>0.3398267999999999</v>
+        <v>0.3681457</v>
       </c>
       <c r="N14">
-        <v>8.245173200000002</v>
+        <v>8.216854300000001</v>
       </c>
       <c r="O14">
-        <v>2.432326094</v>
+        <v>2.4239720185</v>
       </c>
       <c r="P14">
-        <v>5.812847106000001</v>
+        <v>5.792882281500001</v>
       </c>
       <c r="Q14">
-        <v>13.352847106</v>
+        <v>13.3328822815</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1133631409082753</v>
+        <v>0.1139307279056888</v>
       </c>
       <c r="T14">
-        <v>1.045180302197348</v>
+        <v>1.053960692533037</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.26286920278213</v>
+        <v>23.31957157179889</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1037297282779492</v>
+        <v>0.1034445125566161</v>
       </c>
       <c r="C15">
-        <v>49.4567587763861</v>
+        <v>49.05501644802343</v>
       </c>
       <c r="D15">
-        <v>38.1757587763861</v>
+        <v>38.33701644802343</v>
       </c>
       <c r="E15">
-        <v>-5.981000000000001</v>
+        <v>-5.418</v>
       </c>
       <c r="F15">
-        <v>7.319</v>
+        <v>7.882000000000001</v>
       </c>
       <c r="G15">
         <v>18.6</v>
@@ -2505,28 +2505,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M15">
-        <v>0.3681457</v>
+        <v>0.3964646</v>
       </c>
       <c r="N15">
-        <v>8.216854300000001</v>
+        <v>8.188535400000001</v>
       </c>
       <c r="O15">
-        <v>2.4239720185</v>
+        <v>2.415617943</v>
       </c>
       <c r="P15">
-        <v>5.792882281500001</v>
+        <v>5.772917457000001</v>
       </c>
       <c r="Q15">
-        <v>13.3328822815</v>
+        <v>13.312917457</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1139307279056888</v>
+        <v>0.1145115146007164</v>
       </c>
       <c r="T15">
-        <v>1.053960692533037</v>
+        <v>1.062945277992813</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.31957157179889</v>
+        <v>21.65388788809896</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1034445125566161</v>
+        <v>0.1031592968352831</v>
       </c>
       <c r="C16">
-        <v>49.05501644802343</v>
+        <v>48.65464223108695</v>
       </c>
       <c r="D16">
-        <v>38.33701644802343</v>
+        <v>38.49964223108694</v>
       </c>
       <c r="E16">
-        <v>-5.418</v>
+        <v>-4.855</v>
       </c>
       <c r="F16">
-        <v>7.882000000000001</v>
+        <v>8.445</v>
       </c>
       <c r="G16">
         <v>18.6</v>
@@ -2587,28 +2587,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M16">
-        <v>0.3964646</v>
+        <v>0.4247835</v>
       </c>
       <c r="N16">
-        <v>8.188535400000001</v>
+        <v>8.160216500000001</v>
       </c>
       <c r="O16">
-        <v>2.415617943</v>
+        <v>2.4072638675</v>
       </c>
       <c r="P16">
-        <v>5.772917457000001</v>
+        <v>5.7529526325</v>
       </c>
       <c r="Q16">
-        <v>13.312917457</v>
+        <v>13.2929526325</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1145115146007164</v>
+        <v>0.1151059668650389</v>
       </c>
       <c r="T16">
-        <v>1.062945277992813</v>
+        <v>1.072141265463406</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.65388788809896</v>
+        <v>20.2102953622257</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1031592968352831</v>
+        <v>0.10287408111395</v>
       </c>
       <c r="C17">
-        <v>48.65464223108695</v>
+        <v>48.25565361035025</v>
       </c>
       <c r="D17">
-        <v>38.49964223108694</v>
+        <v>38.66365361035025</v>
       </c>
       <c r="E17">
-        <v>-4.855000000000002</v>
+        <v>-4.292000000000002</v>
       </c>
       <c r="F17">
-        <v>8.444999999999999</v>
+        <v>9.007999999999999</v>
       </c>
       <c r="G17">
         <v>18.6</v>
@@ -2669,28 +2669,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M17">
-        <v>0.4247834999999999</v>
+        <v>0.4531024</v>
       </c>
       <c r="N17">
-        <v>8.160216500000001</v>
+        <v>8.1318976</v>
       </c>
       <c r="O17">
-        <v>2.4072638675</v>
+        <v>2.398909792</v>
       </c>
       <c r="P17">
-        <v>5.7529526325</v>
+        <v>5.732987808000001</v>
       </c>
       <c r="Q17">
-        <v>13.2929526325</v>
+        <v>13.272987808</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1151059668650389</v>
+        <v>0.1157145727547024</v>
       </c>
       <c r="T17">
-        <v>1.072141265463406</v>
+        <v>1.081556205016633</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.2102953622257</v>
+        <v>18.9471519020866</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.10287408111395</v>
+        <v>0.1025888653926169</v>
       </c>
       <c r="C18">
-        <v>48.25565361035025</v>
+        <v>47.85806836980741</v>
       </c>
       <c r="D18">
-        <v>38.66365361035025</v>
+        <v>38.8290683698074</v>
       </c>
       <c r="E18">
-        <v>-4.292000000000002</v>
+        <v>-3.729000000000001</v>
       </c>
       <c r="F18">
-        <v>9.007999999999999</v>
+        <v>9.571</v>
       </c>
       <c r="G18">
         <v>18.6</v>
@@ -2751,28 +2751,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M18">
-        <v>0.4531024</v>
+        <v>0.4814212999999999</v>
       </c>
       <c r="N18">
-        <v>8.1318976</v>
+        <v>8.103578700000002</v>
       </c>
       <c r="O18">
-        <v>2.398909792</v>
+        <v>2.3905557165</v>
       </c>
       <c r="P18">
-        <v>5.732987808000001</v>
+        <v>5.713022983500002</v>
       </c>
       <c r="Q18">
-        <v>13.272987808</v>
+        <v>13.2530229835</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1157145727547024</v>
+        <v>0.1163378438465264</v>
       </c>
       <c r="T18">
-        <v>1.081556205016633</v>
+        <v>1.09119801058319</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.9471519020866</v>
+        <v>17.83261355490503</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1025888653926169</v>
+        <v>0.1023036496712838</v>
       </c>
       <c r="C19">
-        <v>47.85806836980741</v>
+        <v>47.46190459910125</v>
       </c>
       <c r="D19">
-        <v>38.8290683698074</v>
+        <v>38.99590459910124</v>
       </c>
       <c r="E19">
-        <v>-3.729000000000001</v>
+        <v>-3.166</v>
       </c>
       <c r="F19">
-        <v>9.571</v>
+        <v>10.134</v>
       </c>
       <c r="G19">
         <v>18.6</v>
@@ -2833,28 +2833,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M19">
-        <v>0.4814212999999999</v>
+        <v>0.5097402</v>
       </c>
       <c r="N19">
-        <v>8.103578700000002</v>
+        <v>8.075259800000001</v>
       </c>
       <c r="O19">
-        <v>2.3905557165</v>
+        <v>2.382201641</v>
       </c>
       <c r="P19">
-        <v>5.713022983500002</v>
+        <v>5.693058159000001</v>
       </c>
       <c r="Q19">
-        <v>13.2530229835</v>
+        <v>13.233058159</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1163378438465264</v>
+        <v>0.1169763166722974</v>
       </c>
       <c r="T19">
-        <v>1.09119801058319</v>
+        <v>1.101074982139176</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.83261355490503</v>
+        <v>16.84191280185475</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1023036496712838</v>
+        <v>0.1020184339499508</v>
       </c>
       <c r="C20">
-        <v>47.46190459910124</v>
+        <v>47.06718070011816</v>
       </c>
       <c r="D20">
-        <v>38.99590459910124</v>
+        <v>39.16418070011815</v>
       </c>
       <c r="E20">
-        <v>-3.166000000000002</v>
+        <v>-2.603000000000002</v>
       </c>
       <c r="F20">
-        <v>10.134</v>
+        <v>10.697</v>
       </c>
       <c r="G20">
         <v>18.6</v>
@@ -2915,28 +2915,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M20">
-        <v>0.5097401999999999</v>
+        <v>0.5380590999999999</v>
       </c>
       <c r="N20">
-        <v>8.075259800000001</v>
+        <v>8.046940900000001</v>
       </c>
       <c r="O20">
-        <v>2.382201641</v>
+        <v>2.3738475655</v>
       </c>
       <c r="P20">
-        <v>5.693058159000001</v>
+        <v>5.673093334500001</v>
       </c>
       <c r="Q20">
-        <v>13.233058159</v>
+        <v>13.2130933345</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1169763166722974</v>
+        <v>0.1176305542591985</v>
       </c>
       <c r="T20">
-        <v>1.101074982139176</v>
+        <v>1.11119582953605</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.84191280185475</v>
+        <v>15.95549633859924</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1020184339499508</v>
+        <v>0.1017332182286177</v>
       </c>
       <c r="C21">
-        <v>47.06718070011816</v>
+        <v>46.67391539375424</v>
       </c>
       <c r="D21">
-        <v>39.16418070011815</v>
+        <v>39.33391539375423</v>
       </c>
       <c r="E21">
-        <v>-2.603000000000002</v>
+        <v>-2.040000000000001</v>
       </c>
       <c r="F21">
-        <v>10.697</v>
+        <v>11.26</v>
       </c>
       <c r="G21">
         <v>18.6</v>
@@ -2997,28 +2997,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M21">
-        <v>0.5380590999999999</v>
+        <v>0.5663779999999999</v>
       </c>
       <c r="N21">
-        <v>8.046940900000001</v>
+        <v>8.018622000000001</v>
       </c>
       <c r="O21">
-        <v>2.3738475655</v>
+        <v>2.36549349</v>
       </c>
       <c r="P21">
-        <v>5.673093334500001</v>
+        <v>5.65312851</v>
       </c>
       <c r="Q21">
-        <v>13.2130933345</v>
+        <v>13.19312851</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1176305542591985</v>
+        <v>0.1183011477857721</v>
       </c>
       <c r="T21">
-        <v>1.11119582953605</v>
+        <v>1.121569698117846</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.95549633859924</v>
+        <v>15.15772152166928</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1017332182286177</v>
+        <v>0.1014480025072846</v>
       </c>
       <c r="C22">
-        <v>46.67391539375424</v>
+        <v>46.28212772685821</v>
       </c>
       <c r="D22">
-        <v>39.33391539375423</v>
+        <v>39.50512772685821</v>
       </c>
       <c r="E22">
-        <v>-2.040000000000001</v>
+        <v>-1.477</v>
       </c>
       <c r="F22">
-        <v>11.26</v>
+        <v>11.823</v>
       </c>
       <c r="G22">
         <v>18.6</v>
@@ -3079,28 +3079,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M22">
-        <v>0.5663779999999999</v>
+        <v>0.5946969</v>
       </c>
       <c r="N22">
-        <v>8.018622000000001</v>
+        <v>7.990303100000001</v>
       </c>
       <c r="O22">
-        <v>2.36549349</v>
+        <v>2.3571394145</v>
       </c>
       <c r="P22">
-        <v>5.65312851</v>
+        <v>5.633163685500001</v>
       </c>
       <c r="Q22">
-        <v>13.19312851</v>
+        <v>13.1731636855</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1183011477857721</v>
+        <v>0.1189887183636514</v>
       </c>
       <c r="T22">
-        <v>1.121569698117846</v>
+        <v>1.132206196283992</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.15772152166928</v>
+        <v>14.43592525873264</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1014480025072846</v>
+        <v>0.1011627867859516</v>
       </c>
       <c r="C23">
-        <v>46.28212772685821</v>
+        <v>45.89183707935642</v>
       </c>
       <c r="D23">
-        <v>39.50512772685821</v>
+        <v>39.67783707935642</v>
       </c>
       <c r="E23">
-        <v>-1.477000000000002</v>
+        <v>-0.9140000000000015</v>
       </c>
       <c r="F23">
-        <v>11.823</v>
+        <v>12.386</v>
       </c>
       <c r="G23">
         <v>18.6</v>
@@ -3161,28 +3161,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M23">
-        <v>0.5946968999999999</v>
+        <v>0.6230157999999999</v>
       </c>
       <c r="N23">
-        <v>7.990303100000001</v>
+        <v>7.961984200000001</v>
       </c>
       <c r="O23">
-        <v>2.3571394145</v>
+        <v>2.348785339</v>
       </c>
       <c r="P23">
-        <v>5.633163685500001</v>
+        <v>5.613198861000001</v>
       </c>
       <c r="Q23">
-        <v>13.1731636855</v>
+        <v>13.153198861</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1189887183636514</v>
+        <v>0.1196939189563481</v>
       </c>
       <c r="T23">
-        <v>1.132206196283992</v>
+        <v>1.143115425172346</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.43592525873265</v>
+        <v>13.77974683788116</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1011627867859516</v>
+        <v>0.1008775710646185</v>
       </c>
       <c r="C24">
-        <v>45.89183707935642</v>
+        <v>45.50306317156573</v>
       </c>
       <c r="D24">
-        <v>39.67783707935642</v>
+        <v>39.85206317156573</v>
       </c>
       <c r="E24">
-        <v>-0.9140000000000015</v>
+        <v>-0.3510000000000009</v>
       </c>
       <c r="F24">
-        <v>12.386</v>
+        <v>12.949</v>
       </c>
       <c r="G24">
         <v>18.6</v>
@@ -3243,28 +3243,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M24">
-        <v>0.6230157999999999</v>
+        <v>0.6513346999999999</v>
       </c>
       <c r="N24">
-        <v>7.961984200000001</v>
+        <v>7.933665300000001</v>
       </c>
       <c r="O24">
-        <v>2.348785339</v>
+        <v>2.3404312635</v>
       </c>
       <c r="P24">
-        <v>5.613198861000001</v>
+        <v>5.593234036500001</v>
       </c>
       <c r="Q24">
-        <v>13.153198861</v>
+        <v>13.1332340365</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1196939189563481</v>
+        <v>0.1204174364475565</v>
       </c>
       <c r="T24">
-        <v>1.143115425172346</v>
+        <v>1.154308010655203</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.77974683788116</v>
+        <v>13.1806274101472</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1008775710646185</v>
+        <v>0.1008461553432854</v>
       </c>
       <c r="C25">
-        <v>45.50306317156573</v>
+        <v>44.95934728566505</v>
       </c>
       <c r="D25">
-        <v>39.85206317156573</v>
+        <v>39.87134728566505</v>
       </c>
       <c r="E25">
-        <v>-0.3510000000000009</v>
+        <v>0.2119999999999997</v>
       </c>
       <c r="F25">
-        <v>12.949</v>
+        <v>13.512</v>
       </c>
       <c r="G25">
         <v>18.6</v>
@@ -3325,45 +3325,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M25">
-        <v>0.6513346999999999</v>
+        <v>0.6999216</v>
       </c>
       <c r="N25">
-        <v>7.933665300000001</v>
+        <v>7.885078400000001</v>
       </c>
       <c r="O25">
-        <v>2.3404312635</v>
+        <v>2.326098128</v>
       </c>
       <c r="P25">
-        <v>5.593234036500001</v>
+        <v>5.558980272000001</v>
       </c>
       <c r="Q25">
-        <v>13.1332340365</v>
+        <v>13.098980272</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1204174364475565</v>
+        <v>0.121159993872744</v>
       </c>
       <c r="T25">
-        <v>1.154308010655203</v>
+        <v>1.165795137861293</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.295</v>
       </c>
       <c r="W25">
-        <v>0.0354615</v>
+        <v>0.036519</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.1806274101472</v>
+        <v>12.26565946814615</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1008461553432854</v>
+        <v>0.1005715146219523</v>
       </c>
       <c r="C26">
-        <v>44.95934728566505</v>
+        <v>44.56572987312768</v>
       </c>
       <c r="D26">
-        <v>39.87134728566505</v>
+        <v>40.04072987312768</v>
       </c>
       <c r="E26">
-        <v>0.211999999999998</v>
+        <v>0.7749999999999986</v>
       </c>
       <c r="F26">
-        <v>13.512</v>
+        <v>14.075</v>
       </c>
       <c r="G26">
         <v>18.6</v>
@@ -3407,28 +3407,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M26">
-        <v>0.6999215999999999</v>
+        <v>0.729085</v>
       </c>
       <c r="N26">
-        <v>7.885078400000001</v>
+        <v>7.855915000000001</v>
       </c>
       <c r="O26">
-        <v>2.326098128</v>
+        <v>2.317494925</v>
       </c>
       <c r="P26">
-        <v>5.558980272000001</v>
+        <v>5.538420075000001</v>
       </c>
       <c r="Q26">
-        <v>13.098980272</v>
+        <v>13.078420075</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.121159993872744</v>
+        <v>0.1219223528292698</v>
       </c>
       <c r="T26">
-        <v>1.165795137861293</v>
+        <v>1.177588588459546</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.26565946814615</v>
+        <v>11.7750330894203</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1005715146219523</v>
+        <v>0.1002968739006193</v>
       </c>
       <c r="C27">
-        <v>44.56572987312768</v>
+        <v>44.17355775233614</v>
       </c>
       <c r="D27">
-        <v>40.04072987312768</v>
+        <v>40.21155775233614</v>
       </c>
       <c r="E27">
-        <v>0.7749999999999986</v>
+        <v>1.337999999999999</v>
       </c>
       <c r="F27">
-        <v>14.075</v>
+        <v>14.638</v>
       </c>
       <c r="G27">
         <v>18.6</v>
@@ -3489,28 +3489,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M27">
-        <v>0.729085</v>
+        <v>0.7582483999999999</v>
       </c>
       <c r="N27">
-        <v>7.855915000000001</v>
+        <v>7.826751600000001</v>
       </c>
       <c r="O27">
-        <v>2.317494925</v>
+        <v>2.308891722</v>
       </c>
       <c r="P27">
-        <v>5.538420075000001</v>
+        <v>5.517859878</v>
       </c>
       <c r="Q27">
-        <v>13.078420075</v>
+        <v>13.057859878</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1219223528292698</v>
+        <v>0.1227053160819179</v>
       </c>
       <c r="T27">
-        <v>1.177588588459546</v>
+        <v>1.189700780965859</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.7750330894203</v>
+        <v>11.32214720136568</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1002968739006193</v>
+        <v>0.1000222331792862</v>
       </c>
       <c r="C28">
-        <v>44.17355775233614</v>
+        <v>43.78284950092252</v>
       </c>
       <c r="D28">
-        <v>40.21155775233614</v>
+        <v>40.38384950092252</v>
       </c>
       <c r="E28">
-        <v>1.337999999999999</v>
+        <v>1.901</v>
       </c>
       <c r="F28">
-        <v>14.638</v>
+        <v>15.201</v>
       </c>
       <c r="G28">
         <v>18.6</v>
@@ -3571,28 +3571,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M28">
-        <v>0.7582483999999999</v>
+        <v>0.7874118</v>
       </c>
       <c r="N28">
-        <v>7.826751600000001</v>
+        <v>7.797588200000001</v>
       </c>
       <c r="O28">
-        <v>2.308891722</v>
+        <v>2.300288519</v>
       </c>
       <c r="P28">
-        <v>5.517859878</v>
+        <v>5.497299681000001</v>
       </c>
       <c r="Q28">
-        <v>13.057859878</v>
+        <v>13.037299681</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1227053160819179</v>
+        <v>0.1235097303825838</v>
       </c>
       <c r="T28">
-        <v>1.189700780965859</v>
+        <v>1.202144814362756</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.32214720136568</v>
+        <v>10.90280841612991</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1000222331792862</v>
+        <v>0.0997475924579531</v>
       </c>
       <c r="C29">
-        <v>43.78284950092252</v>
+        <v>43.39362401628231</v>
       </c>
       <c r="D29">
-        <v>40.38384950092252</v>
+        <v>40.55762401628231</v>
       </c>
       <c r="E29">
-        <v>1.901</v>
+        <v>2.464</v>
       </c>
       <c r="F29">
-        <v>15.201</v>
+        <v>15.764</v>
       </c>
       <c r="G29">
         <v>18.6</v>
@@ -3653,28 +3653,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M29">
-        <v>0.7874118</v>
+        <v>0.8165752000000001</v>
       </c>
       <c r="N29">
-        <v>7.797588200000001</v>
+        <v>7.768424800000001</v>
       </c>
       <c r="O29">
-        <v>2.300288519</v>
+        <v>2.291685316</v>
       </c>
       <c r="P29">
-        <v>5.497299681000001</v>
+        <v>5.476739484000001</v>
       </c>
       <c r="Q29">
-        <v>13.037299681</v>
+        <v>13.016739484</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1235097303825838</v>
+        <v>0.1243364895249349</v>
       </c>
       <c r="T29">
-        <v>1.202144814362756</v>
+        <v>1.214934515354011</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.90280841612991</v>
+        <v>10.51342240126813</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0997475924579531</v>
+        <v>0.09947295173662003</v>
       </c>
       <c r="C30">
-        <v>43.39362401628231</v>
+        <v>43.00590052248391</v>
       </c>
       <c r="D30">
-        <v>40.55762401628231</v>
+        <v>40.73290052248391</v>
       </c>
       <c r="E30">
-        <v>2.464</v>
+        <v>3.027000000000001</v>
       </c>
       <c r="F30">
-        <v>15.764</v>
+        <v>16.327</v>
       </c>
       <c r="G30">
         <v>18.6</v>
@@ -3735,28 +3735,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M30">
-        <v>0.8165752000000001</v>
+        <v>0.8457386000000001</v>
       </c>
       <c r="N30">
-        <v>7.768424800000001</v>
+        <v>7.739261400000001</v>
       </c>
       <c r="O30">
-        <v>2.291685316</v>
+        <v>2.283082113</v>
       </c>
       <c r="P30">
-        <v>5.476739484000001</v>
+        <v>5.456179287000001</v>
       </c>
       <c r="Q30">
-        <v>13.016739484</v>
+        <v>12.996179287</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1243364895249349</v>
+        <v>0.1251865376572113</v>
       </c>
       <c r="T30">
-        <v>1.214934515354011</v>
+        <v>1.228084489612626</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.51342240126813</v>
+        <v>10.15089059432785</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09947295173662003</v>
+        <v>0.09919831101528696</v>
       </c>
       <c r="C31">
-        <v>43.00590052248391</v>
+        <v>42.61969857735816</v>
       </c>
       <c r="D31">
-        <v>40.73290052248391</v>
+        <v>40.90969857735816</v>
       </c>
       <c r="E31">
-        <v>3.026999999999997</v>
+        <v>3.589999999999996</v>
       </c>
       <c r="F31">
-        <v>16.327</v>
+        <v>16.89</v>
       </c>
       <c r="G31">
         <v>18.6</v>
@@ -3817,28 +3817,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M31">
-        <v>0.8457385999999999</v>
+        <v>0.8749019999999998</v>
       </c>
       <c r="N31">
-        <v>7.739261400000001</v>
+        <v>7.710098000000001</v>
       </c>
       <c r="O31">
-        <v>2.283082113</v>
+        <v>2.27447891</v>
       </c>
       <c r="P31">
-        <v>5.456179287000001</v>
+        <v>5.435619090000001</v>
       </c>
       <c r="Q31">
-        <v>12.996179287</v>
+        <v>12.97561909</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1251865376572113</v>
+        <v>0.1260608728789814</v>
       </c>
       <c r="T31">
-        <v>1.228084489612626</v>
+        <v>1.241610177421487</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.15089059432785</v>
+        <v>9.81252757451692</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09919831101528696</v>
+        <v>0.09929520529395387</v>
       </c>
       <c r="C32">
-        <v>42.61969857735816</v>
+        <v>41.99414860900364</v>
       </c>
       <c r="D32">
-        <v>40.90969857735816</v>
+        <v>40.84714860900364</v>
       </c>
       <c r="E32">
-        <v>3.589999999999996</v>
+        <v>4.152999999999999</v>
       </c>
       <c r="F32">
-        <v>16.89</v>
+        <v>17.453</v>
       </c>
       <c r="G32">
         <v>18.6</v>
@@ -3899,45 +3899,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M32">
-        <v>0.8749019999999998</v>
+        <v>0.9337354999999999</v>
       </c>
       <c r="N32">
-        <v>7.710098000000001</v>
+        <v>7.651264500000001</v>
       </c>
       <c r="O32">
-        <v>2.27447891</v>
+        <v>2.2571230275</v>
       </c>
       <c r="P32">
-        <v>5.435619090000001</v>
+        <v>5.394141472500001</v>
       </c>
       <c r="Q32">
-        <v>12.97561909</v>
+        <v>12.9341414725</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1260608728789814</v>
+        <v>0.1269605511506578</v>
       </c>
       <c r="T32">
-        <v>1.241610177421487</v>
+        <v>1.255527914152344</v>
       </c>
       <c r="U32">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V32">
         <v>0.295</v>
       </c>
       <c r="W32">
-        <v>0.036519</v>
+        <v>0.0377175</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>9.81252757451692</v>
+        <v>9.194252547964602</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09929520529395387</v>
+        <v>0.0990325495726208</v>
       </c>
       <c r="C33">
-        <v>41.99414860900364</v>
+        <v>41.60115100315709</v>
       </c>
       <c r="D33">
-        <v>40.84714860900364</v>
+        <v>41.01715100315709</v>
       </c>
       <c r="E33">
-        <v>4.152999999999999</v>
+        <v>4.715999999999998</v>
       </c>
       <c r="F33">
-        <v>17.453</v>
+        <v>18.016</v>
       </c>
       <c r="G33">
         <v>18.6</v>
@@ -3981,28 +3981,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M33">
-        <v>0.9337354999999999</v>
+        <v>0.9638559999999999</v>
       </c>
       <c r="N33">
-        <v>7.651264500000001</v>
+        <v>7.621144000000001</v>
       </c>
       <c r="O33">
-        <v>2.2571230275</v>
+        <v>2.24823748</v>
       </c>
       <c r="P33">
-        <v>5.394141472500001</v>
+        <v>5.372906520000001</v>
       </c>
       <c r="Q33">
-        <v>12.9341414725</v>
+        <v>12.91290652</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1269605511506578</v>
+        <v>0.1278866905479718</v>
       </c>
       <c r="T33">
-        <v>1.255527914152344</v>
+        <v>1.269854996081167</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.194252547964602</v>
+        <v>8.906932155840707</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0990325495726208</v>
+        <v>0.09876989385128773</v>
       </c>
       <c r="C34">
-        <v>41.60115100315709</v>
+        <v>41.2095743826405</v>
       </c>
       <c r="D34">
-        <v>41.01715100315709</v>
+        <v>41.1885743826405</v>
       </c>
       <c r="E34">
-        <v>4.715999999999998</v>
+        <v>5.279</v>
       </c>
       <c r="F34">
-        <v>18.016</v>
+        <v>18.579</v>
       </c>
       <c r="G34">
         <v>18.6</v>
@@ -4063,28 +4063,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M34">
-        <v>0.9638559999999999</v>
+        <v>0.9939765</v>
       </c>
       <c r="N34">
-        <v>7.621144000000001</v>
+        <v>7.5910235</v>
       </c>
       <c r="O34">
-        <v>2.24823748</v>
+        <v>2.2393519325</v>
       </c>
       <c r="P34">
-        <v>5.372906520000001</v>
+        <v>5.3516715675</v>
       </c>
       <c r="Q34">
-        <v>12.91290652</v>
+        <v>12.8916715675</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1278866905479718</v>
+        <v>0.1288404758974444</v>
       </c>
       <c r="T34">
-        <v>1.269854996081167</v>
+        <v>1.284609752097418</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.906932155840707</v>
+        <v>8.637025120815231</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09876989385128773</v>
+        <v>0.09850723812995466</v>
       </c>
       <c r="C35">
-        <v>41.2095743826405</v>
+        <v>40.81943663843941</v>
       </c>
       <c r="D35">
-        <v>41.1885743826405</v>
+        <v>41.36143663843941</v>
       </c>
       <c r="E35">
-        <v>5.279</v>
+        <v>5.841999999999999</v>
       </c>
       <c r="F35">
-        <v>18.579</v>
+        <v>19.142</v>
       </c>
       <c r="G35">
         <v>18.6</v>
@@ -4145,28 +4145,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M35">
-        <v>0.9939765</v>
+        <v>1.024097</v>
       </c>
       <c r="N35">
-        <v>7.5910235</v>
+        <v>7.560903000000001</v>
       </c>
       <c r="O35">
-        <v>2.2393519325</v>
+        <v>2.230466385</v>
       </c>
       <c r="P35">
-        <v>5.3516715675</v>
+        <v>5.330436615</v>
       </c>
       <c r="Q35">
-        <v>12.8916715675</v>
+        <v>12.870436615</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1288404758974444</v>
+        <v>0.1298231638332646</v>
       </c>
       <c r="T35">
-        <v>1.284609752097418</v>
+        <v>1.299811621932343</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.637025120815231</v>
+        <v>8.382994970203018</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09850723812995466</v>
+        <v>0.09824458240862158</v>
       </c>
       <c r="C36">
-        <v>40.81943663843941</v>
+        <v>40.43075596314829</v>
       </c>
       <c r="D36">
-        <v>41.36143663843941</v>
+        <v>41.53575596314828</v>
       </c>
       <c r="E36">
-        <v>5.841999999999999</v>
+        <v>6.405000000000001</v>
       </c>
       <c r="F36">
-        <v>19.142</v>
+        <v>19.705</v>
       </c>
       <c r="G36">
         <v>18.6</v>
@@ -4227,28 +4227,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M36">
-        <v>1.024097</v>
+        <v>1.0542175</v>
       </c>
       <c r="N36">
-        <v>7.560903000000001</v>
+        <v>7.530782500000001</v>
       </c>
       <c r="O36">
-        <v>2.230466385</v>
+        <v>2.2215808375</v>
       </c>
       <c r="P36">
-        <v>5.330436615</v>
+        <v>5.309201662500001</v>
       </c>
       <c r="Q36">
-        <v>12.870436615</v>
+        <v>12.8492016625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1298231638332646</v>
+        <v>0.1308360883209563</v>
       </c>
       <c r="T36">
-        <v>1.299811621932343</v>
+        <v>1.315481241608343</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.382994970203018</v>
+        <v>8.143480828197218</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09824458240862158</v>
+        <v>0.09798192668728851</v>
       </c>
       <c r="C37">
-        <v>40.43075596314829</v>
+        <v>40.04355085735308</v>
       </c>
       <c r="D37">
-        <v>41.53575596314828</v>
+        <v>41.71155085735308</v>
       </c>
       <c r="E37">
-        <v>6.405000000000001</v>
+        <v>6.968</v>
       </c>
       <c r="F37">
-        <v>19.705</v>
+        <v>20.268</v>
       </c>
       <c r="G37">
         <v>18.6</v>
@@ -4309,28 +4309,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M37">
-        <v>1.0542175</v>
+        <v>1.084338</v>
       </c>
       <c r="N37">
-        <v>7.530782500000001</v>
+        <v>7.500662000000001</v>
       </c>
       <c r="O37">
-        <v>2.2215808375</v>
+        <v>2.21269529</v>
       </c>
       <c r="P37">
-        <v>5.309201662500001</v>
+        <v>5.287966710000001</v>
       </c>
       <c r="Q37">
-        <v>12.8492016625</v>
+        <v>12.82796671</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1308360883209563</v>
+        <v>0.1318806666988883</v>
       </c>
       <c r="T37">
-        <v>1.315481241608343</v>
+        <v>1.331640536899218</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.143480828197218</v>
+        <v>7.917273027413962</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0979819266872885</v>
+        <v>0.09771927096595544</v>
       </c>
       <c r="C38">
-        <v>40.0435508573531</v>
+        <v>39.65784013617672</v>
       </c>
       <c r="D38">
-        <v>41.71155085735309</v>
+        <v>41.88884013617672</v>
       </c>
       <c r="E38">
-        <v>6.967999999999996</v>
+        <v>7.530999999999999</v>
       </c>
       <c r="F38">
-        <v>20.268</v>
+        <v>20.831</v>
       </c>
       <c r="G38">
         <v>18.6</v>
@@ -4391,28 +4391,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M38">
-        <v>1.084338</v>
+        <v>1.1144585</v>
       </c>
       <c r="N38">
-        <v>7.500662000000001</v>
+        <v>7.470541500000001</v>
       </c>
       <c r="O38">
-        <v>2.21269529</v>
+        <v>2.2038097425</v>
       </c>
       <c r="P38">
-        <v>5.287966710000001</v>
+        <v>5.266731757500001</v>
       </c>
       <c r="Q38">
-        <v>12.82796671</v>
+        <v>12.8067317575</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1318806666988883</v>
+        <v>0.1329584062951674</v>
       </c>
       <c r="T38">
-        <v>1.331640536899218</v>
+        <v>1.34831282569139</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.917273027413963</v>
+        <v>7.703292675321693</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09771927096595544</v>
+        <v>0.09767093524462236</v>
       </c>
       <c r="C39">
-        <v>39.65784013617672</v>
+        <v>39.12763045505104</v>
       </c>
       <c r="D39">
-        <v>41.88884013617672</v>
+        <v>41.92163045505104</v>
       </c>
       <c r="E39">
-        <v>7.530999999999999</v>
+        <v>8.093999999999998</v>
       </c>
       <c r="F39">
-        <v>20.831</v>
+        <v>21.394</v>
       </c>
       <c r="G39">
         <v>18.6</v>
@@ -4473,45 +4473,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M39">
-        <v>1.1144585</v>
+        <v>1.1616942</v>
       </c>
       <c r="N39">
-        <v>7.470541500000001</v>
+        <v>7.423305800000001</v>
       </c>
       <c r="O39">
-        <v>2.2038097425</v>
+        <v>2.189875211</v>
       </c>
       <c r="P39">
-        <v>5.266731757500001</v>
+        <v>5.233430589000001</v>
       </c>
       <c r="Q39">
-        <v>12.8067317575</v>
+        <v>12.773430589</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1329584062951674</v>
+        <v>0.1340709116848748</v>
       </c>
       <c r="T39">
-        <v>1.34831282569139</v>
+        <v>1.365522930251052</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.295</v>
       </c>
       <c r="W39">
-        <v>0.0377175</v>
+        <v>0.0382815</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.703292675321693</v>
+        <v>7.390068746146794</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09767093524462236</v>
+        <v>0.09741391952328932</v>
       </c>
       <c r="C40">
-        <v>39.12763045505104</v>
+        <v>38.73985236678568</v>
       </c>
       <c r="D40">
-        <v>41.92163045505104</v>
+        <v>42.09685236678568</v>
       </c>
       <c r="E40">
-        <v>8.093999999999998</v>
+        <v>8.657</v>
       </c>
       <c r="F40">
-        <v>21.394</v>
+        <v>21.957</v>
       </c>
       <c r="G40">
         <v>18.6</v>
@@ -4555,28 +4555,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M40">
-        <v>1.1616942</v>
+        <v>1.1922651</v>
       </c>
       <c r="N40">
-        <v>7.423305800000001</v>
+        <v>7.392734900000001</v>
       </c>
       <c r="O40">
-        <v>2.189875211</v>
+        <v>2.1808567955</v>
       </c>
       <c r="P40">
-        <v>5.233430589000001</v>
+        <v>5.2118781045</v>
       </c>
       <c r="Q40">
-        <v>12.773430589</v>
+        <v>12.7518781045</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1340709116848748</v>
+        <v>0.13521989266113</v>
       </c>
       <c r="T40">
-        <v>1.365522930251052</v>
+        <v>1.383297300533981</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.390068746146794</v>
+        <v>7.200579803937901</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09741391952328932</v>
+        <v>0.09715690380195624</v>
       </c>
       <c r="C41">
-        <v>38.73985236678568</v>
+        <v>38.35354519395585</v>
       </c>
       <c r="D41">
-        <v>42.09685236678568</v>
+        <v>42.27354519395585</v>
       </c>
       <c r="E41">
-        <v>8.657</v>
+        <v>9.219999999999999</v>
       </c>
       <c r="F41">
-        <v>21.957</v>
+        <v>22.52</v>
       </c>
       <c r="G41">
         <v>18.6</v>
@@ -4637,28 +4637,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M41">
-        <v>1.1922651</v>
+        <v>1.222836</v>
       </c>
       <c r="N41">
-        <v>7.392734900000001</v>
+        <v>7.362164000000001</v>
       </c>
       <c r="O41">
-        <v>2.1808567955</v>
+        <v>2.17183838</v>
       </c>
       <c r="P41">
-        <v>5.2118781045</v>
+        <v>5.190325620000001</v>
       </c>
       <c r="Q41">
-        <v>12.7518781045</v>
+        <v>12.73032562</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.13521989266113</v>
+        <v>0.1364071730032604</v>
       </c>
       <c r="T41">
-        <v>1.383297300533981</v>
+        <v>1.401664149826342</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.200579803937901</v>
+        <v>7.020565308839452</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09715690380195624</v>
+        <v>0.09689988808062315</v>
       </c>
       <c r="C42">
-        <v>38.35354519395585</v>
+        <v>37.9687275362193</v>
       </c>
       <c r="D42">
-        <v>42.27354519395585</v>
+        <v>42.4517275362193</v>
       </c>
       <c r="E42">
-        <v>9.219999999999999</v>
+        <v>9.783000000000001</v>
       </c>
       <c r="F42">
-        <v>22.52</v>
+        <v>23.083</v>
       </c>
       <c r="G42">
         <v>18.6</v>
@@ -4719,28 +4719,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M42">
-        <v>1.222836</v>
+        <v>1.2534069</v>
       </c>
       <c r="N42">
-        <v>7.362164000000001</v>
+        <v>7.331593100000001</v>
       </c>
       <c r="O42">
-        <v>2.17183838</v>
+        <v>2.1628199645</v>
       </c>
       <c r="P42">
-        <v>5.190325620000001</v>
+        <v>5.1687731355</v>
       </c>
       <c r="Q42">
-        <v>12.73032562</v>
+        <v>12.7087731355</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1364071730032604</v>
+        <v>0.1376347001366494</v>
       </c>
       <c r="T42">
-        <v>1.401664149826342</v>
+        <v>1.42065360417946</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.020565308839452</v>
+        <v>6.849332008623856</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09689988808062315</v>
+        <v>0.09664287235929006</v>
       </c>
       <c r="C43">
-        <v>37.9687275362193</v>
+        <v>37.58541830815025</v>
       </c>
       <c r="D43">
-        <v>42.4517275362193</v>
+        <v>42.63141830815025</v>
       </c>
       <c r="E43">
-        <v>9.783000000000001</v>
+        <v>10.346</v>
       </c>
       <c r="F43">
-        <v>23.083</v>
+        <v>23.646</v>
       </c>
       <c r="G43">
         <v>18.6</v>
@@ -4801,28 +4801,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M43">
-        <v>1.2534069</v>
+        <v>1.2839778</v>
       </c>
       <c r="N43">
-        <v>7.331593100000001</v>
+        <v>7.3010222</v>
       </c>
       <c r="O43">
-        <v>2.1628199645</v>
+        <v>2.153801549</v>
       </c>
       <c r="P43">
-        <v>5.1687731355</v>
+        <v>5.147220651</v>
       </c>
       <c r="Q43">
-        <v>12.7087731355</v>
+        <v>12.687220651</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1376347001366494</v>
+        <v>0.1389045557918794</v>
       </c>
       <c r="T43">
-        <v>1.42065360417946</v>
+        <v>1.440297867303375</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.849332008623856</v>
+        <v>6.686252675085192</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09664287235929009</v>
+        <v>0.09638585663795701</v>
       </c>
       <c r="C44">
-        <v>37.58541830815022</v>
+        <v>37.20363674593257</v>
       </c>
       <c r="D44">
-        <v>42.63141830815022</v>
+        <v>42.81263674593257</v>
       </c>
       <c r="E44">
-        <v>10.346</v>
+        <v>10.909</v>
       </c>
       <c r="F44">
-        <v>23.646</v>
+        <v>24.209</v>
       </c>
       <c r="G44">
         <v>18.6</v>
@@ -4883,28 +4883,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M44">
-        <v>1.2839778</v>
+        <v>1.3145487</v>
       </c>
       <c r="N44">
-        <v>7.301022200000001</v>
+        <v>7.270451300000001</v>
       </c>
       <c r="O44">
-        <v>2.153801549</v>
+        <v>2.1447831335</v>
       </c>
       <c r="P44">
-        <v>5.147220651000001</v>
+        <v>5.125668166500001</v>
       </c>
       <c r="Q44">
-        <v>12.687220651</v>
+        <v>12.6656681665</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1389045557918794</v>
+        <v>0.1402189677858895</v>
       </c>
       <c r="T44">
-        <v>1.440297867303375</v>
+        <v>1.460631402817604</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.686252675085194</v>
+        <v>6.530758426827398</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09638585663795701</v>
+        <v>0.09612884091662394</v>
       </c>
       <c r="C45">
-        <v>37.20363674593257</v>
+        <v>36.82340241422467</v>
       </c>
       <c r="D45">
-        <v>42.81263674593257</v>
+        <v>42.99540241422466</v>
       </c>
       <c r="E45">
-        <v>10.909</v>
+        <v>11.472</v>
       </c>
       <c r="F45">
-        <v>24.209</v>
+        <v>24.772</v>
       </c>
       <c r="G45">
         <v>18.6</v>
@@ -4965,28 +4965,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M45">
-        <v>1.3145487</v>
+        <v>1.3451196</v>
       </c>
       <c r="N45">
-        <v>7.270451300000001</v>
+        <v>7.239880400000001</v>
       </c>
       <c r="O45">
-        <v>2.1447831335</v>
+        <v>2.135764718</v>
       </c>
       <c r="P45">
-        <v>5.125668166500001</v>
+        <v>5.104115682000001</v>
       </c>
       <c r="Q45">
-        <v>12.6656681665</v>
+        <v>12.644115682</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1402189677858895</v>
+        <v>0.1415803230653999</v>
       </c>
       <c r="T45">
-        <v>1.460631402817604</v>
+        <v>1.481691136028769</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.530758426827398</v>
+        <v>6.382332098944957</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09612884091662394</v>
+        <v>0.09587182519529085</v>
       </c>
       <c r="C46">
-        <v>36.82340241422467</v>
+        <v>36.44473521320058</v>
       </c>
       <c r="D46">
-        <v>42.99540241422466</v>
+        <v>43.17973521320058</v>
       </c>
       <c r="E46">
-        <v>11.472</v>
+        <v>12.035</v>
       </c>
       <c r="F46">
-        <v>24.772</v>
+        <v>25.335</v>
       </c>
       <c r="G46">
         <v>18.6</v>
@@ -5047,28 +5047,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M46">
-        <v>1.3451196</v>
+        <v>1.3756905</v>
       </c>
       <c r="N46">
-        <v>7.239880400000001</v>
+        <v>7.209309500000001</v>
       </c>
       <c r="O46">
-        <v>2.135764718</v>
+        <v>2.1267463025</v>
       </c>
       <c r="P46">
-        <v>5.104115682000001</v>
+        <v>5.082563197500001</v>
       </c>
       <c r="Q46">
-        <v>12.644115682</v>
+        <v>12.6225631975</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1415803230653999</v>
+        <v>0.1429911821732561</v>
       </c>
       <c r="T46">
-        <v>1.481691136028769</v>
+        <v>1.503516677720339</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.382332098944957</v>
+        <v>6.24050249674618</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09587182519529085</v>
+        <v>0.0959391094739578</v>
       </c>
       <c r="C47">
-        <v>36.44473521320058</v>
+        <v>35.83332607828117</v>
       </c>
       <c r="D47">
-        <v>43.17973521320058</v>
+        <v>43.13132607828117</v>
       </c>
       <c r="E47">
-        <v>12.035</v>
+        <v>12.598</v>
       </c>
       <c r="F47">
-        <v>25.335</v>
+        <v>25.898</v>
       </c>
       <c r="G47">
         <v>18.6</v>
@@ -5129,45 +5129,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M47">
-        <v>1.3756905</v>
+        <v>1.4321594</v>
       </c>
       <c r="N47">
-        <v>7.209309500000001</v>
+        <v>7.152840600000001</v>
       </c>
       <c r="O47">
-        <v>2.1267463025</v>
+        <v>2.110087977</v>
       </c>
       <c r="P47">
-        <v>5.082563197500001</v>
+        <v>5.042752623000001</v>
       </c>
       <c r="Q47">
-        <v>12.6225631975</v>
+        <v>12.582752623</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1429911821732561</v>
+        <v>0.144454295322144</v>
       </c>
       <c r="T47">
-        <v>1.503516677720339</v>
+        <v>1.526150572807895</v>
       </c>
       <c r="U47">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.295</v>
       </c>
       <c r="W47">
-        <v>0.0382815</v>
+        <v>0.03898650000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>6.24050249674618</v>
+        <v>5.994444473150127</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0959391094739578</v>
+        <v>0.09568914375262472</v>
       </c>
       <c r="C48">
-        <v>35.83332607828117</v>
+        <v>35.4507190545268</v>
       </c>
       <c r="D48">
-        <v>43.13132607828117</v>
+        <v>43.3117190545268</v>
       </c>
       <c r="E48">
-        <v>12.598</v>
+        <v>13.161</v>
       </c>
       <c r="F48">
-        <v>25.898</v>
+        <v>26.461</v>
       </c>
       <c r="G48">
         <v>18.6</v>
@@ -5211,28 +5211,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M48">
-        <v>1.4321594</v>
+        <v>1.4632933</v>
       </c>
       <c r="N48">
-        <v>7.152840600000001</v>
+        <v>7.121706700000001</v>
       </c>
       <c r="O48">
-        <v>2.110087977</v>
+        <v>2.1009034765</v>
       </c>
       <c r="P48">
-        <v>5.042752623000001</v>
+        <v>5.020803223500001</v>
       </c>
       <c r="Q48">
-        <v>12.582752623</v>
+        <v>12.5608032235</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.144454295322144</v>
+        <v>0.1459726202879711</v>
       </c>
       <c r="T48">
-        <v>1.526150572807895</v>
+        <v>1.549638577144037</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.994444473150127</v>
+        <v>5.866903101380974</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09568914375262472</v>
+        <v>0.09543917803129162</v>
       </c>
       <c r="C49">
-        <v>35.4507190545268</v>
+        <v>35.06962732385356</v>
       </c>
       <c r="D49">
-        <v>43.3117190545268</v>
+        <v>43.49362732385356</v>
       </c>
       <c r="E49">
-        <v>13.161</v>
+        <v>13.724</v>
       </c>
       <c r="F49">
-        <v>26.461</v>
+        <v>27.024</v>
       </c>
       <c r="G49">
         <v>18.6</v>
@@ -5293,28 +5293,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M49">
-        <v>1.4632933</v>
+        <v>1.4944272</v>
       </c>
       <c r="N49">
-        <v>7.121706700000001</v>
+        <v>7.0905728</v>
       </c>
       <c r="O49">
-        <v>2.1009034765</v>
+        <v>2.091718976</v>
       </c>
       <c r="P49">
-        <v>5.020803223500001</v>
+        <v>4.998853824</v>
       </c>
       <c r="Q49">
-        <v>12.5608032235</v>
+        <v>12.538853824</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1459726202879711</v>
+        <v>0.1475493423678685</v>
       </c>
       <c r="T49">
-        <v>1.549638577144037</v>
+        <v>1.574029966262338</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.866903101380974</v>
+        <v>5.744675953435537</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09543917803129162</v>
+        <v>0.09518921230995855</v>
       </c>
       <c r="C50">
-        <v>35.06962732385357</v>
+        <v>34.69007005938114</v>
       </c>
       <c r="D50">
-        <v>43.49362732385356</v>
+        <v>43.67707005938114</v>
       </c>
       <c r="E50">
-        <v>13.724</v>
+        <v>14.287</v>
       </c>
       <c r="F50">
-        <v>27.024</v>
+        <v>27.587</v>
       </c>
       <c r="G50">
         <v>18.6</v>
@@ -5375,28 +5375,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M50">
-        <v>1.4944272</v>
+        <v>1.5255611</v>
       </c>
       <c r="N50">
-        <v>7.090572800000001</v>
+        <v>7.059438900000001</v>
       </c>
       <c r="O50">
-        <v>2.091718976</v>
+        <v>2.0825344755</v>
       </c>
       <c r="P50">
-        <v>4.998853824000001</v>
+        <v>4.976904424500001</v>
       </c>
       <c r="Q50">
-        <v>12.538853824</v>
+        <v>12.5169044245</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1475493423678685</v>
+        <v>0.1491878966861932</v>
       </c>
       <c r="T50">
-        <v>1.574029966262338</v>
+        <v>1.599377880444103</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.744675953435538</v>
+        <v>5.627437668671547</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09518921230995855</v>
+        <v>0.09493924658862549</v>
       </c>
       <c r="C51">
-        <v>34.69007005938114</v>
+        <v>34.31206675906463</v>
       </c>
       <c r="D51">
-        <v>43.67707005938114</v>
+        <v>43.86206675906463</v>
       </c>
       <c r="E51">
-        <v>14.287</v>
+        <v>14.85</v>
       </c>
       <c r="F51">
-        <v>27.587</v>
+        <v>28.15</v>
       </c>
       <c r="G51">
         <v>18.6</v>
@@ -5457,28 +5457,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M51">
-        <v>1.5255611</v>
+        <v>1.556695</v>
       </c>
       <c r="N51">
-        <v>7.059438900000001</v>
+        <v>7.028305000000001</v>
       </c>
       <c r="O51">
-        <v>2.0825344755</v>
+        <v>2.073349975</v>
       </c>
       <c r="P51">
-        <v>4.976904424500001</v>
+        <v>4.954955025000001</v>
       </c>
       <c r="Q51">
-        <v>12.5169044245</v>
+        <v>12.494955025</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1491878966861932</v>
+        <v>0.150891993177251</v>
       </c>
       <c r="T51">
-        <v>1.599377880444103</v>
+        <v>1.625739711193138</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.627437668671547</v>
+        <v>5.514888915298116</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09493924658862549</v>
+        <v>0.09468928086729242</v>
       </c>
       <c r="C52">
-        <v>34.31206675906463</v>
+        <v>33.93563725260296</v>
       </c>
       <c r="D52">
-        <v>43.86206675906463</v>
+        <v>44.04863725260296</v>
       </c>
       <c r="E52">
-        <v>14.85</v>
+        <v>15.413</v>
       </c>
       <c r="F52">
-        <v>28.15</v>
+        <v>28.713</v>
       </c>
       <c r="G52">
         <v>18.6</v>
@@ -5539,28 +5539,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M52">
-        <v>1.556695</v>
+        <v>1.5878289</v>
       </c>
       <c r="N52">
-        <v>7.028305000000001</v>
+        <v>6.997171100000001</v>
       </c>
       <c r="O52">
-        <v>2.073349975</v>
+        <v>2.0641654745</v>
       </c>
       <c r="P52">
-        <v>4.954955025000001</v>
+        <v>4.933005625500001</v>
       </c>
       <c r="Q52">
-        <v>12.494955025</v>
+        <v>12.4730056255</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.150891993177251</v>
+        <v>0.1526656446271274</v>
       </c>
       <c r="T52">
-        <v>1.625739711193138</v>
+        <v>1.65317753503397</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.514888915298116</v>
+        <v>5.406753838527565</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09468928086729242</v>
+        <v>0.09443931514595935</v>
       </c>
       <c r="C53">
-        <v>33.93563725260296</v>
+        <v>33.56080170852456</v>
       </c>
       <c r="D53">
-        <v>44.04863725260296</v>
+        <v>44.23680170852456</v>
       </c>
       <c r="E53">
-        <v>15.413</v>
+        <v>15.976</v>
       </c>
       <c r="F53">
-        <v>28.713</v>
+        <v>29.276</v>
       </c>
       <c r="G53">
         <v>18.6</v>
@@ -5621,28 +5621,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M53">
-        <v>1.5878289</v>
+        <v>1.6189628</v>
       </c>
       <c r="N53">
-        <v>6.997171100000001</v>
+        <v>6.966037200000001</v>
       </c>
       <c r="O53">
-        <v>2.0641654745</v>
+        <v>2.054980974</v>
       </c>
       <c r="P53">
-        <v>4.933005625500001</v>
+        <v>4.911056226</v>
       </c>
       <c r="Q53">
-        <v>12.4730056255</v>
+        <v>12.451056226</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1526656446271274</v>
+        <v>0.1545131982207486</v>
       </c>
       <c r="T53">
-        <v>1.65317753503397</v>
+        <v>1.681758601534837</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.406753838527565</v>
+        <v>5.302777803171265</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09443931514595935</v>
+        <v>0.09418934942462628</v>
       </c>
       <c r="C54">
-        <v>33.56080170852456</v>
+        <v>33.1875806414554</v>
       </c>
       <c r="D54">
-        <v>44.23680170852456</v>
+        <v>44.4265806414554</v>
       </c>
       <c r="E54">
-        <v>15.976</v>
+        <v>16.539</v>
       </c>
       <c r="F54">
-        <v>29.276</v>
+        <v>29.839</v>
       </c>
       <c r="G54">
         <v>18.6</v>
@@ -5703,28 +5703,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M54">
-        <v>1.6189628</v>
+        <v>1.6500967</v>
       </c>
       <c r="N54">
-        <v>6.966037200000001</v>
+        <v>6.934903300000001</v>
       </c>
       <c r="O54">
-        <v>2.054980974</v>
+        <v>2.0457964735</v>
       </c>
       <c r="P54">
-        <v>4.911056226</v>
+        <v>4.889106826500001</v>
       </c>
       <c r="Q54">
-        <v>12.451056226</v>
+        <v>12.4291068265</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1545131982207486</v>
+        <v>0.1564393711162261</v>
       </c>
       <c r="T54">
-        <v>1.681758601534837</v>
+        <v>1.711555883631485</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.302777803171265</v>
+        <v>5.202725391790676</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09418934942462628</v>
+        <v>0.0939393837032932</v>
       </c>
       <c r="C55">
-        <v>33.1875806414554</v>
+        <v>32.81599491957486</v>
       </c>
       <c r="D55">
-        <v>44.4265806414554</v>
+        <v>44.61799491957485</v>
       </c>
       <c r="E55">
-        <v>16.539</v>
+        <v>17.102</v>
       </c>
       <c r="F55">
-        <v>29.839</v>
+        <v>30.402</v>
       </c>
       <c r="G55">
         <v>18.6</v>
@@ -5785,28 +5785,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M55">
-        <v>1.6500967</v>
+        <v>1.6812306</v>
       </c>
       <c r="N55">
-        <v>6.934903300000001</v>
+        <v>6.903769400000001</v>
       </c>
       <c r="O55">
-        <v>2.0457964735</v>
+        <v>2.036611973</v>
       </c>
       <c r="P55">
-        <v>4.889106826500001</v>
+        <v>4.867157427</v>
       </c>
       <c r="Q55">
-        <v>12.4291068265</v>
+        <v>12.407157427</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1564393711162261</v>
+        <v>0.1584492906593331</v>
       </c>
       <c r="T55">
-        <v>1.711555883631485</v>
+        <v>1.742648699732336</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.202725391790676</v>
+        <v>5.106378625276033</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0939393837032932</v>
+        <v>0.09368941798196012</v>
       </c>
       <c r="C56">
-        <v>32.81599491957486</v>
+        <v>32.4460657722652</v>
       </c>
       <c r="D56">
-        <v>44.61799491957485</v>
+        <v>44.8110657722652</v>
       </c>
       <c r="E56">
-        <v>17.102</v>
+        <v>17.665</v>
       </c>
       <c r="F56">
-        <v>30.402</v>
+        <v>30.965</v>
       </c>
       <c r="G56">
         <v>18.6</v>
@@ -5867,28 +5867,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M56">
-        <v>1.6812306</v>
+        <v>1.7123645</v>
       </c>
       <c r="N56">
-        <v>6.903769400000001</v>
+        <v>6.872635500000001</v>
       </c>
       <c r="O56">
-        <v>2.036611973</v>
+        <v>2.0274274725</v>
       </c>
       <c r="P56">
-        <v>4.867157427</v>
+        <v>4.845208027500001</v>
       </c>
       <c r="Q56">
-        <v>12.407157427</v>
+        <v>12.3852080275</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1584492906593331</v>
+        <v>0.1605485399599114</v>
       </c>
       <c r="T56">
-        <v>1.742648699732336</v>
+        <v>1.775123418771002</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.106378625276033</v>
+        <v>5.013535377543742</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09368941798196012</v>
+        <v>0.09343945226062705</v>
       </c>
       <c r="C57">
-        <v>32.4460657722652</v>
+        <v>32.0778147979605</v>
       </c>
       <c r="D57">
-        <v>44.8110657722652</v>
+        <v>45.0058147979605</v>
       </c>
       <c r="E57">
-        <v>17.665</v>
+        <v>18.228</v>
       </c>
       <c r="F57">
-        <v>30.965</v>
+        <v>31.528</v>
       </c>
       <c r="G57">
         <v>18.6</v>
@@ -5949,28 +5949,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M57">
-        <v>1.7123645</v>
+        <v>1.7434984</v>
       </c>
       <c r="N57">
-        <v>6.872635500000001</v>
+        <v>6.841501600000001</v>
       </c>
       <c r="O57">
-        <v>2.0274274725</v>
+        <v>2.018242972</v>
       </c>
       <c r="P57">
-        <v>4.845208027500001</v>
+        <v>4.823258628</v>
       </c>
       <c r="Q57">
-        <v>12.3852080275</v>
+        <v>12.363258628</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1605485399599114</v>
+        <v>0.1627432096832433</v>
       </c>
       <c r="T57">
-        <v>1.775123418771002</v>
+        <v>1.809074261402335</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.013535377543742</v>
+        <v>4.924007960087604</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09343945226062705</v>
+        <v>0.09318948653929399</v>
       </c>
       <c r="C58">
-        <v>32.0778147979605</v>
+        <v>31.71126397220122</v>
       </c>
       <c r="D58">
-        <v>45.0058147979605</v>
+        <v>45.20226397220122</v>
       </c>
       <c r="E58">
-        <v>18.228</v>
+        <v>18.791</v>
       </c>
       <c r="F58">
-        <v>31.528</v>
+        <v>32.091</v>
       </c>
       <c r="G58">
         <v>18.6</v>
@@ -6031,28 +6031,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M58">
-        <v>1.7434984</v>
+        <v>1.7746323</v>
       </c>
       <c r="N58">
-        <v>6.841501600000001</v>
+        <v>6.8103677</v>
       </c>
       <c r="O58">
-        <v>2.018242972</v>
+        <v>2.0090584715</v>
       </c>
       <c r="P58">
-        <v>4.823258628</v>
+        <v>4.801309228500001</v>
       </c>
       <c r="Q58">
-        <v>12.363258628</v>
+        <v>12.3413092285</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1627432096832433</v>
+        <v>0.1650399570681255</v>
       </c>
       <c r="T58">
-        <v>1.809074261402335</v>
+        <v>1.844604212993264</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.924007960087604</v>
+        <v>4.837621855524663</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09318948653929399</v>
+        <v>0.09293952081796092</v>
       </c>
       <c r="C59">
-        <v>31.71126397220122</v>
+        <v>31.34643565590053</v>
       </c>
       <c r="D59">
-        <v>45.20226397220122</v>
+        <v>45.40043565590052</v>
       </c>
       <c r="E59">
-        <v>18.791</v>
+        <v>19.354</v>
       </c>
       <c r="F59">
-        <v>32.091</v>
+        <v>32.654</v>
       </c>
       <c r="G59">
         <v>18.6</v>
@@ -6113,28 +6113,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M59">
-        <v>1.7746323</v>
+        <v>1.8057662</v>
       </c>
       <c r="N59">
-        <v>6.8103677</v>
+        <v>6.7792338</v>
       </c>
       <c r="O59">
-        <v>2.0090584715</v>
+        <v>1.999873971</v>
       </c>
       <c r="P59">
-        <v>4.801309228500001</v>
+        <v>4.779359829000001</v>
       </c>
       <c r="Q59">
-        <v>12.3413092285</v>
+        <v>12.319359829</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1650399570681255</v>
+        <v>0.1674460733760974</v>
       </c>
       <c r="T59">
-        <v>1.844604212993264</v>
+        <v>1.881826067040905</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.837621855524663</v>
+        <v>4.754214582153548</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09293952081796091</v>
+        <v>0.09268955509662782</v>
       </c>
       <c r="C60">
-        <v>31.34643565590055</v>
+        <v>30.98335260382909</v>
       </c>
       <c r="D60">
-        <v>45.40043565590054</v>
+        <v>45.60035260382909</v>
       </c>
       <c r="E60">
-        <v>19.354</v>
+        <v>19.917</v>
       </c>
       <c r="F60">
-        <v>32.654</v>
+        <v>33.217</v>
       </c>
       <c r="G60">
         <v>18.6</v>
@@ -6195,28 +6195,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M60">
-        <v>1.8057662</v>
+        <v>1.8369001</v>
       </c>
       <c r="N60">
-        <v>6.779233800000001</v>
+        <v>6.748099900000001</v>
       </c>
       <c r="O60">
-        <v>1.999873971</v>
+        <v>1.9906894705</v>
       </c>
       <c r="P60">
-        <v>4.779359829000001</v>
+        <v>4.7574104295</v>
       </c>
       <c r="Q60">
-        <v>12.319359829</v>
+        <v>12.2974104295</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1674460733760974</v>
+        <v>0.1699695612112874</v>
       </c>
       <c r="T60">
-        <v>1.881826067040905</v>
+        <v>1.920863621285991</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.754214582153549</v>
+        <v>4.673634673981454</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09268955509662782</v>
+        <v>0.09243958937529476</v>
       </c>
       <c r="C61">
-        <v>30.98335260382909</v>
+        <v>30.62203797332497</v>
       </c>
       <c r="D61">
-        <v>45.60035260382909</v>
+        <v>45.80203797332496</v>
       </c>
       <c r="E61">
-        <v>19.917</v>
+        <v>20.47999999999999</v>
       </c>
       <c r="F61">
-        <v>33.217</v>
+        <v>33.77999999999999</v>
       </c>
       <c r="G61">
         <v>18.6</v>
@@ -6277,28 +6277,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M61">
-        <v>1.8369001</v>
+        <v>1.868034</v>
       </c>
       <c r="N61">
-        <v>6.748099900000001</v>
+        <v>6.716966000000001</v>
       </c>
       <c r="O61">
-        <v>1.9906894705</v>
+        <v>1.98150497</v>
       </c>
       <c r="P61">
-        <v>4.7574104295</v>
+        <v>4.735461030000001</v>
       </c>
       <c r="Q61">
-        <v>12.2974104295</v>
+        <v>12.27546103</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1699695612112874</v>
+        <v>0.1726192234382369</v>
       </c>
       <c r="T61">
-        <v>1.920863621285991</v>
+        <v>1.961853053243332</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.673634673981454</v>
+        <v>4.595740762748431</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09243958937529476</v>
+        <v>0.09218962365396169</v>
       </c>
       <c r="C62">
-        <v>30.62203797332497</v>
+        <v>30.26251533323585</v>
       </c>
       <c r="D62">
-        <v>45.80203797332496</v>
+        <v>46.00551533323583</v>
       </c>
       <c r="E62">
-        <v>20.47999999999999</v>
+        <v>21.043</v>
       </c>
       <c r="F62">
-        <v>33.77999999999999</v>
+        <v>34.343</v>
       </c>
       <c r="G62">
         <v>18.6</v>
@@ -6359,28 +6359,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M62">
-        <v>1.868034</v>
+        <v>1.8991679</v>
       </c>
       <c r="N62">
-        <v>6.716966000000001</v>
+        <v>6.685832100000001</v>
       </c>
       <c r="O62">
-        <v>1.98150497</v>
+        <v>1.9723204695</v>
       </c>
       <c r="P62">
-        <v>4.735461030000001</v>
+        <v>4.713511630500001</v>
       </c>
       <c r="Q62">
-        <v>12.27546103</v>
+        <v>12.2535116305</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1726192234382369</v>
+        <v>0.1754047657793889</v>
       </c>
       <c r="T62">
-        <v>1.961853053243332</v>
+        <v>2.004944507352331</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.595740762748431</v>
+        <v>4.520400750244358</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09218962365396169</v>
+        <v>0.09303240793262861</v>
       </c>
       <c r="C63">
-        <v>30.26251533323585</v>
+        <v>29.02059262721758</v>
       </c>
       <c r="D63">
-        <v>46.00551533323583</v>
+        <v>45.32659262721758</v>
       </c>
       <c r="E63">
-        <v>21.043</v>
+        <v>21.606</v>
       </c>
       <c r="F63">
-        <v>34.343</v>
+        <v>34.906</v>
       </c>
       <c r="G63">
         <v>18.6</v>
@@ -6441,45 +6441,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M63">
-        <v>1.8991679</v>
+        <v>2.0175668</v>
       </c>
       <c r="N63">
-        <v>6.685832100000001</v>
+        <v>6.567433200000001</v>
       </c>
       <c r="O63">
-        <v>1.9723204695</v>
+        <v>1.937392794</v>
       </c>
       <c r="P63">
-        <v>4.713511630500001</v>
+        <v>4.630040406000001</v>
       </c>
       <c r="Q63">
-        <v>12.2535116305</v>
+        <v>12.170040406</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1754047657793889</v>
+        <v>0.1783369156121805</v>
       </c>
       <c r="T63">
-        <v>2.004944507352331</v>
+        <v>2.050303932730225</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.295</v>
       </c>
       <c r="W63">
-        <v>0.03898650000000001</v>
+        <v>0.04074900000000001</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.520400750244358</v>
+        <v>4.255125530416143</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09303240793262861</v>
+        <v>0.09280006721129552</v>
       </c>
       <c r="C64">
-        <v>29.02059262721758</v>
+        <v>28.6427507990748</v>
       </c>
       <c r="D64">
-        <v>45.32659262721758</v>
+        <v>45.5117507990748</v>
       </c>
       <c r="E64">
-        <v>21.606</v>
+        <v>22.169</v>
       </c>
       <c r="F64">
-        <v>34.906</v>
+        <v>35.469</v>
       </c>
       <c r="G64">
         <v>18.6</v>
@@ -6523,28 +6523,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M64">
-        <v>2.0175668</v>
+        <v>2.0501082</v>
       </c>
       <c r="N64">
-        <v>6.567433200000001</v>
+        <v>6.5348918</v>
       </c>
       <c r="O64">
-        <v>1.937392794</v>
+        <v>1.927793081</v>
       </c>
       <c r="P64">
-        <v>4.630040406000001</v>
+        <v>4.607098719000001</v>
       </c>
       <c r="Q64">
-        <v>12.170040406</v>
+        <v>12.147098719</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1783369156121805</v>
+        <v>0.1814275600305285</v>
       </c>
       <c r="T64">
-        <v>2.050303932730225</v>
+        <v>2.098115218939356</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.255125530416143</v>
+        <v>4.187583855330172</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09280006721129552</v>
+        <v>0.09256772648996248</v>
       </c>
       <c r="C65">
-        <v>28.6427507990748</v>
+        <v>28.26642791019563</v>
       </c>
       <c r="D65">
-        <v>45.5117507990748</v>
+        <v>45.69842791019563</v>
       </c>
       <c r="E65">
-        <v>22.169</v>
+        <v>22.732</v>
       </c>
       <c r="F65">
-        <v>35.469</v>
+        <v>36.032</v>
       </c>
       <c r="G65">
         <v>18.6</v>
@@ -6605,28 +6605,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M65">
-        <v>2.0501082</v>
+        <v>2.0826496</v>
       </c>
       <c r="N65">
-        <v>6.5348918</v>
+        <v>6.502350400000001</v>
       </c>
       <c r="O65">
-        <v>1.927793081</v>
+        <v>1.918193368</v>
       </c>
       <c r="P65">
-        <v>4.607098719000001</v>
+        <v>4.584157032</v>
       </c>
       <c r="Q65">
-        <v>12.147098719</v>
+        <v>12.124157032</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1814275600305285</v>
+        <v>0.1846899069165624</v>
       </c>
       <c r="T65">
-        <v>2.098115218939356</v>
+        <v>2.148582687715662</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.187583855330172</v>
+        <v>4.122152857590639</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09256772648996248</v>
+        <v>0.09233538576862939</v>
       </c>
       <c r="C66">
-        <v>28.26642791019563</v>
+        <v>27.89164272841681</v>
       </c>
       <c r="D66">
-        <v>45.69842791019563</v>
+        <v>45.88664272841681</v>
       </c>
       <c r="E66">
-        <v>22.732</v>
+        <v>23.295</v>
       </c>
       <c r="F66">
-        <v>36.032</v>
+        <v>36.595</v>
       </c>
       <c r="G66">
         <v>18.6</v>
@@ -6687,28 +6687,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M66">
-        <v>2.0826496</v>
+        <v>2.115191</v>
       </c>
       <c r="N66">
-        <v>6.502350400000001</v>
+        <v>6.469809000000001</v>
       </c>
       <c r="O66">
-        <v>1.918193368</v>
+        <v>1.908593655</v>
       </c>
       <c r="P66">
-        <v>4.584157032</v>
+        <v>4.561215345000001</v>
       </c>
       <c r="Q66">
-        <v>12.124157032</v>
+        <v>12.101215345</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1846899069165624</v>
+        <v>0.1881386736246554</v>
       </c>
       <c r="T66">
-        <v>2.148582687715662</v>
+        <v>2.201934011850613</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.122152857590639</v>
+        <v>4.058735121320013</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09233538576862939</v>
+        <v>0.09373159504729632</v>
       </c>
       <c r="C67">
-        <v>27.89164272841681</v>
+        <v>26.22037156115392</v>
       </c>
       <c r="D67">
-        <v>45.88664272841681</v>
+        <v>44.77837156115392</v>
       </c>
       <c r="E67">
-        <v>23.295</v>
+        <v>23.858</v>
       </c>
       <c r="F67">
-        <v>36.595</v>
+        <v>37.158</v>
       </c>
       <c r="G67">
         <v>18.6</v>
@@ -6769,45 +6769,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M67">
-        <v>2.115191</v>
+        <v>2.2777854</v>
       </c>
       <c r="N67">
-        <v>6.469809000000001</v>
+        <v>6.307214600000001</v>
       </c>
       <c r="O67">
-        <v>1.908593655</v>
+        <v>1.860628307</v>
       </c>
       <c r="P67">
-        <v>4.561215345000001</v>
+        <v>4.446586293000001</v>
       </c>
       <c r="Q67">
-        <v>12.101215345</v>
+        <v>11.986586293</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1881386736246554</v>
+        <v>0.1917903089626362</v>
       </c>
       <c r="T67">
-        <v>2.201934011850613</v>
+        <v>2.258423649169974</v>
       </c>
       <c r="U67">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V67">
         <v>0.295</v>
       </c>
       <c r="W67">
-        <v>0.04074900000000001</v>
+        <v>0.0432165</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.058735121320013</v>
+        <v>3.769011777843514</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09373159504729632</v>
+        <v>0.09352392932596323</v>
       </c>
       <c r="C68">
-        <v>26.22037156115392</v>
+        <v>25.81880937651746</v>
       </c>
       <c r="D68">
-        <v>44.77837156115392</v>
+        <v>44.93980937651747</v>
       </c>
       <c r="E68">
-        <v>23.858</v>
+        <v>24.421</v>
       </c>
       <c r="F68">
-        <v>37.158</v>
+        <v>37.721</v>
       </c>
       <c r="G68">
         <v>18.6</v>
@@ -6851,28 +6851,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M68">
-        <v>2.2777854</v>
+        <v>2.3122973</v>
       </c>
       <c r="N68">
-        <v>6.307214600000001</v>
+        <v>6.2727027</v>
       </c>
       <c r="O68">
-        <v>1.860628307</v>
+        <v>1.8504472965</v>
       </c>
       <c r="P68">
-        <v>4.446586293000001</v>
+        <v>4.4222554035</v>
       </c>
       <c r="Q68">
-        <v>11.986586293</v>
+        <v>11.9622554035</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1917903089626362</v>
+        <v>0.1956632555332219</v>
       </c>
       <c r="T68">
-        <v>2.258423649169974</v>
+        <v>2.318336900872326</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.769011777843514</v>
+        <v>3.712757870711521</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09352392932596323</v>
+        <v>0.09331626360463018</v>
       </c>
       <c r="C69">
-        <v>25.81880937651746</v>
+        <v>25.41841545540971</v>
       </c>
       <c r="D69">
-        <v>44.93980937651747</v>
+        <v>45.10241545540971</v>
       </c>
       <c r="E69">
-        <v>24.421</v>
+        <v>24.984</v>
       </c>
       <c r="F69">
-        <v>37.721</v>
+        <v>38.284</v>
       </c>
       <c r="G69">
         <v>18.6</v>
@@ -6933,28 +6933,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M69">
-        <v>2.3122973</v>
+        <v>2.3468092</v>
       </c>
       <c r="N69">
-        <v>6.2727027</v>
+        <v>6.238190800000001</v>
       </c>
       <c r="O69">
-        <v>1.8504472965</v>
+        <v>1.840266286</v>
       </c>
       <c r="P69">
-        <v>4.4222554035</v>
+        <v>4.397924514000001</v>
       </c>
       <c r="Q69">
-        <v>11.9622554035</v>
+        <v>11.937924514</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1956632555332219</v>
+        <v>0.1997782612644693</v>
       </c>
       <c r="T69">
-        <v>2.318336900872326</v>
+        <v>2.381994730806075</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.712757870711521</v>
+        <v>3.658158490259882</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09331626360463018</v>
+        <v>0.0931085978832971</v>
       </c>
       <c r="C70">
-        <v>25.41841545540971</v>
+        <v>25.01920252529494</v>
       </c>
       <c r="D70">
-        <v>45.10241545540971</v>
+        <v>45.26620252529494</v>
       </c>
       <c r="E70">
-        <v>24.984</v>
+        <v>25.547</v>
       </c>
       <c r="F70">
-        <v>38.284</v>
+        <v>38.847</v>
       </c>
       <c r="G70">
         <v>18.6</v>
@@ -7015,28 +7015,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M70">
-        <v>2.3468092</v>
+        <v>2.3813211</v>
       </c>
       <c r="N70">
-        <v>6.238190800000001</v>
+        <v>6.203678900000001</v>
       </c>
       <c r="O70">
-        <v>1.840266286</v>
+        <v>1.8300852755</v>
       </c>
       <c r="P70">
-        <v>4.397924514000001</v>
+        <v>4.373593624500001</v>
       </c>
       <c r="Q70">
-        <v>11.937924514</v>
+        <v>11.9135936245</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1997782612644693</v>
+        <v>0.2041587512364423</v>
       </c>
       <c r="T70">
-        <v>2.381994730806075</v>
+        <v>2.449759517509743</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.658158490259882</v>
+        <v>3.60514170054597</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0931085978832971</v>
+        <v>0.092900932161964</v>
       </c>
       <c r="C71">
-        <v>25.01920252529494</v>
+        <v>24.62118349918773</v>
       </c>
       <c r="D71">
-        <v>45.26620252529494</v>
+        <v>45.43118349918774</v>
       </c>
       <c r="E71">
-        <v>25.547</v>
+        <v>26.11</v>
       </c>
       <c r="F71">
-        <v>38.847</v>
+        <v>39.41</v>
       </c>
       <c r="G71">
         <v>18.6</v>
@@ -7097,28 +7097,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M71">
-        <v>2.3813211</v>
+        <v>2.415833</v>
       </c>
       <c r="N71">
-        <v>6.203678900000001</v>
+        <v>6.169167000000001</v>
       </c>
       <c r="O71">
-        <v>1.8300852755</v>
+        <v>1.819904265</v>
       </c>
       <c r="P71">
-        <v>4.373593624500001</v>
+        <v>4.349262735000001</v>
       </c>
       <c r="Q71">
-        <v>11.9135936245</v>
+        <v>11.889262735</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2041587512364423</v>
+        <v>0.2088312738732134</v>
       </c>
       <c r="T71">
-        <v>2.449759517509743</v>
+        <v>2.522041956660322</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.60514170054597</v>
+        <v>3.553639676252456</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.092900932161964</v>
+        <v>0.09269326644063094</v>
       </c>
       <c r="C72">
-        <v>24.62118349918773</v>
+        <v>24.22437147904667</v>
       </c>
       <c r="D72">
-        <v>45.43118349918774</v>
+        <v>45.59737147904666</v>
       </c>
       <c r="E72">
-        <v>26.11</v>
+        <v>26.673</v>
       </c>
       <c r="F72">
-        <v>39.41</v>
+        <v>39.973</v>
       </c>
       <c r="G72">
         <v>18.6</v>
@@ -7179,28 +7179,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M72">
-        <v>2.415833</v>
+        <v>2.4503449</v>
       </c>
       <c r="N72">
-        <v>6.169167000000001</v>
+        <v>6.134655100000001</v>
       </c>
       <c r="O72">
-        <v>1.819904265</v>
+        <v>1.8097232545</v>
       </c>
       <c r="P72">
-        <v>4.349262735000001</v>
+        <v>4.3249318455</v>
       </c>
       <c r="Q72">
-        <v>11.889262735</v>
+        <v>11.8649318455</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2088312738732134</v>
+        <v>0.2138260394504516</v>
       </c>
       <c r="T72">
-        <v>2.522041956660322</v>
+        <v>2.599309391614391</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.553639676252456</v>
+        <v>3.503588413206647</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09269326644063094</v>
+        <v>0.09390688071929788</v>
       </c>
       <c r="C73">
-        <v>24.22437147904667</v>
+        <v>22.70700572318781</v>
       </c>
       <c r="D73">
-        <v>45.59737147904666</v>
+        <v>44.6430057231878</v>
       </c>
       <c r="E73">
-        <v>26.673</v>
+        <v>27.23599999999999</v>
       </c>
       <c r="F73">
-        <v>39.973</v>
+        <v>40.53599999999999</v>
       </c>
       <c r="G73">
         <v>18.6</v>
@@ -7261,45 +7261,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M73">
-        <v>2.4503449</v>
+        <v>2.5983576</v>
       </c>
       <c r="N73">
-        <v>6.134655100000001</v>
+        <v>5.986642400000001</v>
       </c>
       <c r="O73">
-        <v>1.8097232545</v>
+        <v>1.766059508</v>
       </c>
       <c r="P73">
-        <v>4.3249318455</v>
+        <v>4.220582892000001</v>
       </c>
       <c r="Q73">
-        <v>11.8649318455</v>
+        <v>11.760582892</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2138260394504515</v>
+        <v>0.2191775739974924</v>
       </c>
       <c r="T73">
-        <v>2.59930939161439</v>
+        <v>2.682095929065177</v>
       </c>
       <c r="U73">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.295</v>
       </c>
       <c r="W73">
-        <v>0.0432165</v>
+        <v>0.04519050000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.503588413206647</v>
+        <v>3.304010194747637</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09390688071929788</v>
+        <v>0.0937189549979648</v>
       </c>
       <c r="C74">
-        <v>22.70700572318781</v>
+        <v>22.28916468544299</v>
       </c>
       <c r="D74">
-        <v>44.6430057231878</v>
+        <v>44.78816468544299</v>
       </c>
       <c r="E74">
-        <v>27.23599999999999</v>
+        <v>27.799</v>
       </c>
       <c r="F74">
-        <v>40.53599999999999</v>
+        <v>41.099</v>
       </c>
       <c r="G74">
         <v>18.6</v>
@@ -7343,28 +7343,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M74">
-        <v>2.5983576</v>
+        <v>2.6344459</v>
       </c>
       <c r="N74">
-        <v>5.986642400000001</v>
+        <v>5.950554100000002</v>
       </c>
       <c r="O74">
-        <v>1.766059508</v>
+        <v>1.7554134595</v>
       </c>
       <c r="P74">
-        <v>4.220582892000001</v>
+        <v>4.195140640500001</v>
       </c>
       <c r="Q74">
-        <v>11.760582892</v>
+        <v>11.7351406405</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2191775739974924</v>
+        <v>0.2249255185109807</v>
       </c>
       <c r="T74">
-        <v>2.682095929065177</v>
+        <v>2.771014802623429</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.304010194747637</v>
+        <v>3.258749781120957</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0937189549979648</v>
+        <v>0.09353102927663173</v>
       </c>
       <c r="C75">
-        <v>22.28916468544299</v>
+        <v>21.87227071034757</v>
       </c>
       <c r="D75">
-        <v>44.78816468544299</v>
+        <v>44.93427071034757</v>
       </c>
       <c r="E75">
-        <v>27.799</v>
+        <v>28.362</v>
       </c>
       <c r="F75">
-        <v>41.099</v>
+        <v>41.662</v>
       </c>
       <c r="G75">
         <v>18.6</v>
@@ -7425,28 +7425,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M75">
-        <v>2.6344459</v>
+        <v>2.6705342</v>
       </c>
       <c r="N75">
-        <v>5.950554100000002</v>
+        <v>5.9144658</v>
       </c>
       <c r="O75">
-        <v>1.7554134595</v>
+        <v>1.744767411</v>
       </c>
       <c r="P75">
-        <v>4.195140640500001</v>
+        <v>4.169698389000001</v>
       </c>
       <c r="Q75">
-        <v>11.7351406405</v>
+        <v>11.709698389</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2249255185109807</v>
+        <v>0.2311156126024297</v>
       </c>
       <c r="T75">
-        <v>2.771014802623429</v>
+        <v>2.866773589532316</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.258749781120957</v>
+        <v>3.214712621916619</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09353102927663173</v>
+        <v>0.09334310355529865</v>
       </c>
       <c r="C76">
-        <v>21.87227071034757</v>
+        <v>21.45633309663665</v>
       </c>
       <c r="D76">
-        <v>44.93427071034757</v>
+        <v>45.08133309663664</v>
       </c>
       <c r="E76">
-        <v>28.362</v>
+        <v>28.92499999999999</v>
       </c>
       <c r="F76">
-        <v>41.662</v>
+        <v>42.22499999999999</v>
       </c>
       <c r="G76">
         <v>18.6</v>
@@ -7507,28 +7507,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M76">
-        <v>2.6705342</v>
+        <v>2.7066225</v>
       </c>
       <c r="N76">
-        <v>5.9144658</v>
+        <v>5.878377500000001</v>
       </c>
       <c r="O76">
-        <v>1.744767411</v>
+        <v>1.7341213625</v>
       </c>
       <c r="P76">
-        <v>4.169698389000001</v>
+        <v>4.144256137500001</v>
       </c>
       <c r="Q76">
-        <v>11.709698389</v>
+        <v>11.6842561375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2311156126024297</v>
+        <v>0.2378009142211946</v>
       </c>
       <c r="T76">
-        <v>2.866773589532316</v>
+        <v>2.970193079393914</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.214712621916619</v>
+        <v>3.171849786957731</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09334310355529865</v>
+        <v>0.09315517783396558</v>
       </c>
       <c r="C77">
-        <v>21.45633309663665</v>
+        <v>21.04136126517783</v>
       </c>
       <c r="D77">
-        <v>45.08133309663664</v>
+        <v>45.22936126517783</v>
       </c>
       <c r="E77">
-        <v>28.92499999999999</v>
+        <v>29.488</v>
       </c>
       <c r="F77">
-        <v>42.22499999999999</v>
+        <v>42.788</v>
       </c>
       <c r="G77">
         <v>18.6</v>
@@ -7589,28 +7589,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M77">
-        <v>2.7066225</v>
+        <v>2.7427108</v>
       </c>
       <c r="N77">
-        <v>5.878377500000001</v>
+        <v>5.842289200000002</v>
       </c>
       <c r="O77">
-        <v>1.7341213625</v>
+        <v>1.723475314</v>
       </c>
       <c r="P77">
-        <v>4.144256137500001</v>
+        <v>4.118813886000002</v>
       </c>
       <c r="Q77">
-        <v>11.6842561375</v>
+        <v>11.658813886</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2378009142211946</v>
+        <v>0.2450433243081899</v>
       </c>
       <c r="T77">
-        <v>2.970193079393914</v>
+        <v>3.082230860077313</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.171849786957731</v>
+        <v>3.130114921339866</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09315517783396558</v>
+        <v>0.09296725211263251</v>
       </c>
       <c r="C78">
-        <v>21.04136126517783</v>
+        <v>20.62736476098316</v>
       </c>
       <c r="D78">
-        <v>45.22936126517783</v>
+        <v>45.37836476098315</v>
       </c>
       <c r="E78">
-        <v>29.488</v>
+        <v>30.051</v>
       </c>
       <c r="F78">
-        <v>42.788</v>
+        <v>43.351</v>
       </c>
       <c r="G78">
         <v>18.6</v>
@@ -7671,28 +7671,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M78">
-        <v>2.7427108</v>
+        <v>2.7787991</v>
       </c>
       <c r="N78">
-        <v>5.842289200000002</v>
+        <v>5.8062009</v>
       </c>
       <c r="O78">
-        <v>1.723475314</v>
+        <v>1.7128292655</v>
       </c>
       <c r="P78">
-        <v>4.118813886000002</v>
+        <v>4.0933716345</v>
       </c>
       <c r="Q78">
-        <v>11.658813886</v>
+        <v>11.6333716345</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2450433243081899</v>
+        <v>0.2529155091853587</v>
       </c>
       <c r="T78">
-        <v>3.082230860077313</v>
+        <v>3.20401105647231</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.130114921339866</v>
+        <v>3.089464078205582</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09296725211263251</v>
+        <v>0.09277932639129943</v>
       </c>
       <c r="C79">
-        <v>20.62736476098316</v>
+        <v>20.21435325526058</v>
       </c>
       <c r="D79">
-        <v>45.37836476098315</v>
+        <v>45.52835325526057</v>
       </c>
       <c r="E79">
-        <v>30.051</v>
+        <v>30.614</v>
       </c>
       <c r="F79">
-        <v>43.351</v>
+        <v>43.914</v>
       </c>
       <c r="G79">
         <v>18.6</v>
@@ -7753,28 +7753,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M79">
-        <v>2.7787991</v>
+        <v>2.8148874</v>
       </c>
       <c r="N79">
-        <v>5.8062009</v>
+        <v>5.770112600000001</v>
       </c>
       <c r="O79">
-        <v>1.7128292655</v>
+        <v>1.702183217</v>
       </c>
       <c r="P79">
-        <v>4.0933716345</v>
+        <v>4.067929383000001</v>
       </c>
       <c r="Q79">
-        <v>11.6333716345</v>
+        <v>11.607929383</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2529155091853587</v>
+        <v>0.2615033472331793</v>
       </c>
       <c r="T79">
-        <v>3.20401105647231</v>
+        <v>3.336862179812308</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.089464078205582</v>
+        <v>3.049855564382433</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09277932639129943</v>
+        <v>0.09259140066996635</v>
       </c>
       <c r="C80">
-        <v>20.21435325526058</v>
+        <v>19.80233654750655</v>
       </c>
       <c r="D80">
-        <v>45.52835325526057</v>
+        <v>45.67933654750655</v>
       </c>
       <c r="E80">
-        <v>30.614</v>
+        <v>31.177</v>
       </c>
       <c r="F80">
-        <v>43.914</v>
+        <v>44.477</v>
       </c>
       <c r="G80">
         <v>18.6</v>
@@ -7835,28 +7835,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M80">
-        <v>2.8148874</v>
+        <v>2.8509757</v>
       </c>
       <c r="N80">
-        <v>5.770112600000001</v>
+        <v>5.734024300000002</v>
       </c>
       <c r="O80">
-        <v>1.702183217</v>
+        <v>1.6915371685</v>
       </c>
       <c r="P80">
-        <v>4.067929383000001</v>
+        <v>4.042487131500001</v>
       </c>
       <c r="Q80">
-        <v>11.607929383</v>
+        <v>11.5824871315</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2615033472331793</v>
+        <v>0.2709090746188874</v>
       </c>
       <c r="T80">
-        <v>3.336862179812308</v>
+        <v>3.482365791089449</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.049855564382433</v>
+        <v>3.011249797744682</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09259140066996635</v>
+        <v>0.09680267494863329</v>
       </c>
       <c r="C81">
-        <v>19.80233654750655</v>
+        <v>16.07951502431769</v>
       </c>
       <c r="D81">
-        <v>45.67933654750655</v>
+        <v>42.51951502431768</v>
       </c>
       <c r="E81">
-        <v>31.177</v>
+        <v>31.74</v>
       </c>
       <c r="F81">
-        <v>44.477</v>
+        <v>45.04</v>
       </c>
       <c r="G81">
         <v>18.6</v>
@@ -7917,45 +7917,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M81">
-        <v>2.8509757</v>
+        <v>3.238376</v>
       </c>
       <c r="N81">
-        <v>5.734024300000002</v>
+        <v>5.346624</v>
       </c>
       <c r="O81">
-        <v>1.6915371685</v>
+        <v>1.57725408</v>
       </c>
       <c r="P81">
-        <v>4.042487131500001</v>
+        <v>3.76936992</v>
       </c>
       <c r="Q81">
-        <v>11.5824871315</v>
+        <v>11.30936992</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2709090746188874</v>
+        <v>0.2812553747431664</v>
       </c>
       <c r="T81">
-        <v>3.482365791089449</v>
+        <v>3.642419763494303</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.295</v>
       </c>
       <c r="W81">
-        <v>0.04519050000000001</v>
+        <v>0.05068950000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.011249797744682</v>
+        <v>2.651020140959543</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09680267494863329</v>
+        <v>0.09666973922730021</v>
       </c>
       <c r="C82">
-        <v>16.07951502431769</v>
+        <v>15.60956335669913</v>
       </c>
       <c r="D82">
-        <v>42.51951502431768</v>
+        <v>42.61256335669913</v>
       </c>
       <c r="E82">
-        <v>31.74</v>
+        <v>32.303</v>
       </c>
       <c r="F82">
-        <v>45.04</v>
+        <v>45.603</v>
       </c>
       <c r="G82">
         <v>18.6</v>
@@ -7999,28 +7999,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M82">
-        <v>3.238376</v>
+        <v>3.2788557</v>
       </c>
       <c r="N82">
-        <v>5.346624</v>
+        <v>5.306144300000001</v>
       </c>
       <c r="O82">
-        <v>1.57725408</v>
+        <v>1.5653125685</v>
       </c>
       <c r="P82">
-        <v>3.76936992</v>
+        <v>3.740831731500001</v>
       </c>
       <c r="Q82">
-        <v>11.30936992</v>
+        <v>11.2808317315</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2812553747431664</v>
+        <v>0.2926907590910537</v>
       </c>
       <c r="T82">
-        <v>3.642419763494303</v>
+        <v>3.819321522468089</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.651020140959543</v>
+        <v>2.618291497243993</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09666973922730021</v>
+        <v>0.09653680350596713</v>
       </c>
       <c r="C83">
-        <v>15.60956335669913</v>
+        <v>15.14001983016958</v>
       </c>
       <c r="D83">
-        <v>42.61256335669913</v>
+        <v>42.70601983016958</v>
       </c>
       <c r="E83">
-        <v>32.303</v>
+        <v>32.866</v>
       </c>
       <c r="F83">
-        <v>45.603</v>
+        <v>46.166</v>
       </c>
       <c r="G83">
         <v>18.6</v>
@@ -8081,28 +8081,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M83">
-        <v>3.2788557</v>
+        <v>3.3193354</v>
       </c>
       <c r="N83">
-        <v>5.306144300000001</v>
+        <v>5.265664600000001</v>
       </c>
       <c r="O83">
-        <v>1.5653125685</v>
+        <v>1.553371057</v>
       </c>
       <c r="P83">
-        <v>3.740831731500001</v>
+        <v>3.712293543000001</v>
       </c>
       <c r="Q83">
-        <v>11.2808317315</v>
+        <v>11.252293543</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2926907590910537</v>
+        <v>0.3053967416998175</v>
       </c>
       <c r="T83">
-        <v>3.819321522468089</v>
+        <v>4.015879032438963</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.618291497243993</v>
+        <v>2.586361113131261</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09653680350596713</v>
+        <v>0.09640386778463408</v>
       </c>
       <c r="C84">
-        <v>15.14001983016958</v>
+        <v>14.67088713599627</v>
       </c>
       <c r="D84">
-        <v>42.70601983016958</v>
+        <v>42.79988713599627</v>
       </c>
       <c r="E84">
-        <v>32.866</v>
+        <v>33.429</v>
       </c>
       <c r="F84">
-        <v>46.166</v>
+        <v>46.729</v>
       </c>
       <c r="G84">
         <v>18.6</v>
@@ -8163,28 +8163,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M84">
-        <v>3.3193354</v>
+        <v>3.3598151</v>
       </c>
       <c r="N84">
-        <v>5.265664600000001</v>
+        <v>5.2251849</v>
       </c>
       <c r="O84">
-        <v>1.553371057</v>
+        <v>1.5414295455</v>
       </c>
       <c r="P84">
-        <v>3.712293543000001</v>
+        <v>3.683755354500001</v>
       </c>
       <c r="Q84">
-        <v>11.252293543</v>
+        <v>11.2237553545</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3053967416998175</v>
+        <v>0.3195975457919652</v>
       </c>
       <c r="T84">
-        <v>4.015879032438963</v>
+        <v>4.235560955347588</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.586361113131261</v>
+        <v>2.555200135864619</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09640386778463408</v>
+        <v>0.09627093206330101</v>
       </c>
       <c r="C85">
-        <v>14.67088713599627</v>
+        <v>14.20216798916012</v>
       </c>
       <c r="D85">
-        <v>42.79988713599627</v>
+        <v>42.89416798916012</v>
       </c>
       <c r="E85">
-        <v>33.429</v>
+        <v>33.992</v>
       </c>
       <c r="F85">
-        <v>46.729</v>
+        <v>47.292</v>
       </c>
       <c r="G85">
         <v>18.6</v>
@@ -8245,28 +8245,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M85">
-        <v>3.3598151</v>
+        <v>3.4002948</v>
       </c>
       <c r="N85">
-        <v>5.2251849</v>
+        <v>5.184705200000001</v>
       </c>
       <c r="O85">
-        <v>1.5414295455</v>
+        <v>1.529488034</v>
       </c>
       <c r="P85">
-        <v>3.683755354500001</v>
+        <v>3.655217166000001</v>
       </c>
       <c r="Q85">
-        <v>11.2237553545</v>
+        <v>11.195217166</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3195975457919652</v>
+        <v>0.3355734503956314</v>
       </c>
       <c r="T85">
-        <v>4.235560955347588</v>
+        <v>4.482703118619791</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.555200135864619</v>
+        <v>2.524781086628136</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09627093206330101</v>
+        <v>0.09847507134196792</v>
       </c>
       <c r="C86">
-        <v>14.20216798916013</v>
+        <v>12.12770642525502</v>
       </c>
       <c r="D86">
-        <v>42.89416798916012</v>
+        <v>41.38270642525502</v>
       </c>
       <c r="E86">
-        <v>33.99199999999999</v>
+        <v>34.55499999999999</v>
       </c>
       <c r="F86">
-        <v>47.29199999999999</v>
+        <v>47.855</v>
       </c>
       <c r="G86">
         <v>18.6</v>
@@ -8327,45 +8327,45 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M86">
-        <v>3.4002948</v>
+        <v>3.627409</v>
       </c>
       <c r="N86">
-        <v>5.184705200000002</v>
+        <v>4.957591000000001</v>
       </c>
       <c r="O86">
-        <v>1.529488034</v>
+        <v>1.462489345</v>
       </c>
       <c r="P86">
-        <v>3.655217166000001</v>
+        <v>3.495101655000001</v>
       </c>
       <c r="Q86">
-        <v>11.195217166</v>
+        <v>11.035101655</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3355734503956311</v>
+        <v>0.3536794756131194</v>
       </c>
       <c r="T86">
-        <v>4.482703118619788</v>
+        <v>4.762797570328283</v>
       </c>
       <c r="U86">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.295</v>
       </c>
       <c r="W86">
-        <v>0.05068950000000001</v>
+        <v>0.05343900000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.524781086628137</v>
+        <v>2.366703065466288</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09847507134196792</v>
+        <v>0.09836963062063483</v>
       </c>
       <c r="C87">
-        <v>12.12770642525502</v>
+        <v>11.63458109549522</v>
       </c>
       <c r="D87">
-        <v>41.38270642525502</v>
+        <v>41.45258109549522</v>
       </c>
       <c r="E87">
-        <v>34.55499999999999</v>
+        <v>35.11799999999999</v>
       </c>
       <c r="F87">
-        <v>47.855</v>
+        <v>48.418</v>
       </c>
       <c r="G87">
         <v>18.6</v>
@@ -8409,28 +8409,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M87">
-        <v>3.627409</v>
+        <v>3.6700844</v>
       </c>
       <c r="N87">
-        <v>4.957591000000001</v>
+        <v>4.9149156</v>
       </c>
       <c r="O87">
-        <v>1.462489345</v>
+        <v>1.449900102</v>
       </c>
       <c r="P87">
-        <v>3.495101655000001</v>
+        <v>3.465015498000001</v>
       </c>
       <c r="Q87">
-        <v>11.035101655</v>
+        <v>11.005015498</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3536794756131194</v>
+        <v>0.3743720758616774</v>
       </c>
       <c r="T87">
-        <v>4.762797570328283</v>
+        <v>5.082905515137991</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.366703065466288</v>
+        <v>2.33918326237947</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09836963062063483</v>
+        <v>0.09826418989930177</v>
       </c>
       <c r="C88">
-        <v>11.63458109549522</v>
+        <v>11.14169213150042</v>
       </c>
       <c r="D88">
-        <v>41.45258109549522</v>
+        <v>41.52269213150041</v>
       </c>
       <c r="E88">
-        <v>35.11799999999999</v>
+        <v>35.681</v>
       </c>
       <c r="F88">
-        <v>48.418</v>
+        <v>48.98099999999999</v>
       </c>
       <c r="G88">
         <v>18.6</v>
@@ -8491,28 +8491,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M88">
-        <v>3.6700844</v>
+        <v>3.7127598</v>
       </c>
       <c r="N88">
-        <v>4.9149156</v>
+        <v>4.872240200000001</v>
       </c>
       <c r="O88">
-        <v>1.449900102</v>
+        <v>1.437310859</v>
       </c>
       <c r="P88">
-        <v>3.465015498000001</v>
+        <v>3.434929341000001</v>
       </c>
       <c r="Q88">
-        <v>11.005015498</v>
+        <v>10.974929341</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3743720758616774</v>
+        <v>0.398248153071552</v>
       </c>
       <c r="T88">
-        <v>5.082905515137991</v>
+        <v>5.452260836072271</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.33918326237947</v>
+        <v>2.312296098444074</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09826418989930177</v>
+        <v>0.0981587491779687</v>
       </c>
       <c r="C89">
-        <v>11.14169213150042</v>
+        <v>10.64904073463791</v>
       </c>
       <c r="D89">
-        <v>41.52269213150041</v>
+        <v>41.5930407346379</v>
       </c>
       <c r="E89">
-        <v>35.681</v>
+        <v>36.244</v>
       </c>
       <c r="F89">
-        <v>48.98099999999999</v>
+        <v>49.544</v>
       </c>
       <c r="G89">
         <v>18.6</v>
@@ -8573,28 +8573,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M89">
-        <v>3.7127598</v>
+        <v>3.7554352</v>
       </c>
       <c r="N89">
-        <v>4.872240200000001</v>
+        <v>4.829564800000001</v>
       </c>
       <c r="O89">
-        <v>1.437310859</v>
+        <v>1.424721616</v>
       </c>
       <c r="P89">
-        <v>3.434929341000001</v>
+        <v>3.404843184000001</v>
       </c>
       <c r="Q89">
-        <v>10.974929341</v>
+        <v>10.944843184</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.398248153071552</v>
+        <v>0.4261035764830725</v>
       </c>
       <c r="T89">
-        <v>5.452260836072271</v>
+        <v>5.883175377162264</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.312296098444074</v>
+        <v>2.286020006416301</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0981587491779687</v>
+        <v>0.09805330845663562</v>
       </c>
       <c r="C90">
-        <v>10.64904073463791</v>
+        <v>10.15662811443033</v>
       </c>
       <c r="D90">
-        <v>41.5930407346379</v>
+        <v>41.66362811443033</v>
       </c>
       <c r="E90">
-        <v>36.244</v>
+        <v>36.807</v>
       </c>
       <c r="F90">
-        <v>49.544</v>
+        <v>50.107</v>
       </c>
       <c r="G90">
         <v>18.6</v>
@@ -8655,28 +8655,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M90">
-        <v>3.7554352</v>
+        <v>3.7981106</v>
       </c>
       <c r="N90">
-        <v>4.829564800000001</v>
+        <v>4.786889400000001</v>
       </c>
       <c r="O90">
-        <v>1.424721616</v>
+        <v>1.412132373</v>
       </c>
       <c r="P90">
-        <v>3.404843184000001</v>
+        <v>3.374757027</v>
       </c>
       <c r="Q90">
-        <v>10.944843184</v>
+        <v>10.914757027</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4261035764830725</v>
+        <v>0.4590236223330511</v>
       </c>
       <c r="T90">
-        <v>5.883175377162264</v>
+        <v>6.392438016632255</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.286020006416301</v>
+        <v>2.260334388366679</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09805330845663562</v>
+        <v>0.09794786773530255</v>
       </c>
       <c r="C91">
-        <v>10.15662811443033</v>
+        <v>9.664455488624995</v>
       </c>
       <c r="D91">
-        <v>41.66362811443033</v>
+        <v>41.734455488625</v>
       </c>
       <c r="E91">
-        <v>36.807</v>
+        <v>37.37</v>
       </c>
       <c r="F91">
-        <v>50.107</v>
+        <v>50.67</v>
       </c>
       <c r="G91">
         <v>18.6</v>
@@ -8737,28 +8737,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M91">
-        <v>3.7981106</v>
+        <v>3.840786</v>
       </c>
       <c r="N91">
-        <v>4.786889400000001</v>
+        <v>4.744214</v>
       </c>
       <c r="O91">
-        <v>1.412132373</v>
+        <v>1.39954313</v>
       </c>
       <c r="P91">
-        <v>3.374757027</v>
+        <v>3.34467087</v>
       </c>
       <c r="Q91">
-        <v>10.914757027</v>
+        <v>10.88467087</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4590236223330511</v>
+        <v>0.4985276773530255</v>
       </c>
       <c r="T91">
-        <v>6.392438016632255</v>
+        <v>7.003553183996245</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.260334388366679</v>
+        <v>2.235219561829271</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09794786773530255</v>
+        <v>0.09784242701396949</v>
       </c>
       <c r="C92">
-        <v>9.664455488624995</v>
+        <v>9.172524083263859</v>
       </c>
       <c r="D92">
-        <v>41.734455488625</v>
+        <v>41.80552408326385</v>
       </c>
       <c r="E92">
-        <v>37.37</v>
+        <v>37.93299999999999</v>
       </c>
       <c r="F92">
-        <v>50.67</v>
+        <v>51.233</v>
       </c>
       <c r="G92">
         <v>18.6</v>
@@ -8819,28 +8819,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M92">
-        <v>3.840786</v>
+        <v>3.8834614</v>
       </c>
       <c r="N92">
-        <v>4.744214</v>
+        <v>4.701538600000001</v>
       </c>
       <c r="O92">
-        <v>1.39954313</v>
+        <v>1.386953887</v>
       </c>
       <c r="P92">
-        <v>3.34467087</v>
+        <v>3.314584713000001</v>
       </c>
       <c r="Q92">
-        <v>10.88467087</v>
+        <v>10.854584713</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4985276773530255</v>
+        <v>0.5468104112663277</v>
       </c>
       <c r="T92">
-        <v>7.003553183996245</v>
+        <v>7.750471721885568</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.235219561829271</v>
+        <v>2.210656709501477</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09784242701396949</v>
+        <v>0.09773698629263641</v>
       </c>
       <c r="C93">
-        <v>9.172524083263859</v>
+        <v>8.68083513275436</v>
       </c>
       <c r="D93">
-        <v>41.80552408326385</v>
+        <v>41.87683513275436</v>
       </c>
       <c r="E93">
-        <v>37.93299999999999</v>
+        <v>38.496</v>
       </c>
       <c r="F93">
-        <v>51.233</v>
+        <v>51.796</v>
       </c>
       <c r="G93">
         <v>18.6</v>
@@ -8901,28 +8901,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M93">
-        <v>3.8834614</v>
+        <v>3.9261368</v>
       </c>
       <c r="N93">
-        <v>4.701538600000001</v>
+        <v>4.658863200000001</v>
       </c>
       <c r="O93">
-        <v>1.386953887</v>
+        <v>1.374364644</v>
       </c>
       <c r="P93">
-        <v>3.314584713000001</v>
+        <v>3.284498556000001</v>
       </c>
       <c r="Q93">
-        <v>10.854584713</v>
+        <v>10.824498556</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5468104112663277</v>
+        <v>0.6071638286579553</v>
       </c>
       <c r="T93">
-        <v>7.750471721885568</v>
+        <v>8.684119894247219</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.210656709501477</v>
+        <v>2.186627832224287</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09773698629263641</v>
+        <v>0.09763154557130332</v>
       </c>
       <c r="C94">
-        <v>8.68083513275436</v>
+        <v>8.189389879940819</v>
       </c>
       <c r="D94">
-        <v>41.87683513275436</v>
+        <v>41.94838987994082</v>
       </c>
       <c r="E94">
-        <v>38.496</v>
+        <v>39.059</v>
       </c>
       <c r="F94">
-        <v>51.796</v>
+        <v>52.359</v>
       </c>
       <c r="G94">
         <v>18.6</v>
@@ -8983,28 +8983,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M94">
-        <v>3.9261368</v>
+        <v>3.9688122</v>
       </c>
       <c r="N94">
-        <v>4.658863200000001</v>
+        <v>4.616187800000001</v>
       </c>
       <c r="O94">
-        <v>1.374364644</v>
+        <v>1.361775401</v>
       </c>
       <c r="P94">
-        <v>3.284498556000001</v>
+        <v>3.254412399</v>
       </c>
       <c r="Q94">
-        <v>10.824498556</v>
+        <v>10.794412399</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6071638286579553</v>
+        <v>0.6847610795900479</v>
       </c>
       <c r="T94">
-        <v>8.684119894247219</v>
+        <v>9.88452468728363</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.186627832224287</v>
+        <v>2.163115704996069</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09763154557130332</v>
+        <v>0.09752610484997026</v>
       </c>
       <c r="C95">
-        <v>8.189389879940819</v>
+        <v>7.698189576176659</v>
       </c>
       <c r="D95">
-        <v>41.94838987994082</v>
+        <v>42.02018957617666</v>
       </c>
       <c r="E95">
-        <v>39.059</v>
+        <v>39.622</v>
       </c>
       <c r="F95">
-        <v>52.359</v>
+        <v>52.922</v>
       </c>
       <c r="G95">
         <v>18.6</v>
@@ -9065,28 +9065,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M95">
-        <v>3.9688122</v>
+        <v>4.0114876</v>
       </c>
       <c r="N95">
-        <v>4.616187800000001</v>
+        <v>4.573512400000001</v>
       </c>
       <c r="O95">
-        <v>1.361775401</v>
+        <v>1.349186158</v>
       </c>
       <c r="P95">
-        <v>3.254412399</v>
+        <v>3.224326242000001</v>
       </c>
       <c r="Q95">
-        <v>10.794412399</v>
+        <v>10.764326242</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6847610795900479</v>
+        <v>0.7882240808328381</v>
       </c>
       <c r="T95">
-        <v>9.88452468728363</v>
+        <v>11.48506441133218</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.163115704996069</v>
+        <v>2.140103835793984</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09752610484997026</v>
+        <v>0.09742066412863717</v>
       </c>
       <c r="C96">
-        <v>7.698189576176659</v>
+        <v>7.20723548139739</v>
       </c>
       <c r="D96">
-        <v>42.02018957617666</v>
+        <v>42.09223548139739</v>
       </c>
       <c r="E96">
-        <v>39.622</v>
+        <v>40.185</v>
       </c>
       <c r="F96">
-        <v>52.922</v>
+        <v>53.485</v>
       </c>
       <c r="G96">
         <v>18.6</v>
@@ -9147,28 +9147,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M96">
-        <v>4.0114876</v>
+        <v>4.054163</v>
       </c>
       <c r="N96">
-        <v>4.573512400000001</v>
+        <v>4.530837000000001</v>
       </c>
       <c r="O96">
-        <v>1.349186158</v>
+        <v>1.336596915</v>
       </c>
       <c r="P96">
-        <v>3.224326242000001</v>
+        <v>3.194240085000001</v>
       </c>
       <c r="Q96">
-        <v>10.764326242</v>
+        <v>10.734240085</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7882240808328381</v>
+        <v>0.9330722825727448</v>
       </c>
       <c r="T96">
-        <v>11.48506441133218</v>
+        <v>13.72582002500015</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.140103835793984</v>
+        <v>2.117576426996152</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09742066412863717</v>
+        <v>0.09731522340730411</v>
       </c>
       <c r="C97">
-        <v>7.20723548139739</v>
+        <v>6.716528864194217</v>
       </c>
       <c r="D97">
-        <v>42.09223548139739</v>
+        <v>42.16452886419422</v>
       </c>
       <c r="E97">
-        <v>40.185</v>
+        <v>40.748</v>
       </c>
       <c r="F97">
-        <v>53.485</v>
+        <v>54.048</v>
       </c>
       <c r="G97">
         <v>18.6</v>
@@ -9229,28 +9229,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M97">
-        <v>4.054163</v>
+        <v>4.0968384</v>
       </c>
       <c r="N97">
-        <v>4.530837000000001</v>
+        <v>4.488161600000001</v>
       </c>
       <c r="O97">
-        <v>1.336596915</v>
+        <v>1.324007672</v>
       </c>
       <c r="P97">
-        <v>3.194240085000001</v>
+        <v>3.164153928000001</v>
       </c>
       <c r="Q97">
-        <v>10.734240085</v>
+        <v>10.704153928</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9330722825727448</v>
+        <v>1.150344585182605</v>
       </c>
       <c r="T97">
-        <v>13.72582002500015</v>
+        <v>17.0869534455021</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.117576426996152</v>
+        <v>2.095518339214942</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09731522340730411</v>
+        <v>0.09720978268597105</v>
       </c>
       <c r="C98">
-        <v>6.716528864194224</v>
+        <v>6.226071001888606</v>
       </c>
       <c r="D98">
-        <v>42.16452886419422</v>
+        <v>42.2370710018886</v>
       </c>
       <c r="E98">
-        <v>40.74799999999999</v>
+        <v>41.31099999999999</v>
       </c>
       <c r="F98">
-        <v>54.04799999999999</v>
+        <v>54.611</v>
       </c>
       <c r="G98">
         <v>18.6</v>
@@ -9311,28 +9311,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M98">
-        <v>4.0968384</v>
+        <v>4.1395138</v>
       </c>
       <c r="N98">
-        <v>4.488161600000001</v>
+        <v>4.4454862</v>
       </c>
       <c r="O98">
-        <v>1.324007672</v>
+        <v>1.311418429</v>
       </c>
       <c r="P98">
-        <v>3.164153928000001</v>
+        <v>3.134067771000001</v>
       </c>
       <c r="Q98">
-        <v>10.704153928</v>
+        <v>10.674067771</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.150344585182602</v>
+        <v>1.512465089532367</v>
       </c>
       <c r="T98">
-        <v>17.08695344550205</v>
+        <v>22.68884247967195</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.095518339214942</v>
+        <v>2.073915057367365</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09720978268597105</v>
+        <v>0.09710434196463796</v>
       </c>
       <c r="C99">
-        <v>6.226071001888606</v>
+        <v>5.735863180607474</v>
       </c>
       <c r="D99">
-        <v>42.2370710018886</v>
+        <v>42.30986318060747</v>
       </c>
       <c r="E99">
-        <v>41.31099999999999</v>
+        <v>41.874</v>
       </c>
       <c r="F99">
-        <v>54.611</v>
+        <v>55.174</v>
       </c>
       <c r="G99">
         <v>18.6</v>
@@ -9393,28 +9393,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M99">
-        <v>4.1395138</v>
+        <v>4.182189200000001</v>
       </c>
       <c r="N99">
-        <v>4.4454862</v>
+        <v>4.4028108</v>
       </c>
       <c r="O99">
-        <v>1.311418429</v>
+        <v>1.298829186</v>
       </c>
       <c r="P99">
-        <v>3.134067771000001</v>
+        <v>3.103981614</v>
       </c>
       <c r="Q99">
-        <v>10.674067771</v>
+        <v>10.643981614</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.512465089532367</v>
+        <v>2.236706098231896</v>
       </c>
       <c r="T99">
-        <v>22.68884247967195</v>
+        <v>33.89262054801175</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.073915057367365</v>
+        <v>2.0527526588228</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09710434196463796</v>
+        <v>0.0969989012433049</v>
       </c>
       <c r="C100">
-        <v>5.735863180607474</v>
+        <v>5.245906695359118</v>
       </c>
       <c r="D100">
-        <v>42.30986318060747</v>
+        <v>42.38290669535911</v>
       </c>
       <c r="E100">
-        <v>41.874</v>
+        <v>42.437</v>
       </c>
       <c r="F100">
-        <v>55.174</v>
+        <v>55.73699999999999</v>
       </c>
       <c r="G100">
         <v>18.6</v>
@@ -9475,28 +9475,28 @@
         <v>8.585000000000001</v>
       </c>
       <c r="M100">
-        <v>4.182189200000001</v>
+        <v>4.2248646</v>
       </c>
       <c r="N100">
-        <v>4.4028108</v>
+        <v>4.360135400000001</v>
       </c>
       <c r="O100">
-        <v>1.298829186</v>
+        <v>1.286239943</v>
       </c>
       <c r="P100">
-        <v>3.103981614</v>
+        <v>3.073895457000001</v>
       </c>
       <c r="Q100">
-        <v>10.643981614</v>
+        <v>10.613895457</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.236706098231896</v>
+        <v>4.409429124330485</v>
       </c>
       <c r="T100">
-        <v>33.89262054801175</v>
+        <v>67.50395475303114</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.0527526588228</v>
+        <v>2.032017783481156</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.0969989012433049</v>
-      </c>
-      <c r="C101">
-        <v>5.245906695359118</v>
-      </c>
-      <c r="D101">
-        <v>42.38290669535911</v>
-      </c>
-      <c r="E101">
-        <v>42.437</v>
-      </c>
-      <c r="F101">
-        <v>55.73699999999999</v>
-      </c>
-      <c r="G101">
-        <v>18.6</v>
-      </c>
-      <c r="H101">
-        <v>43</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>16.125</v>
-      </c>
-      <c r="K101">
-        <v>7.54</v>
-      </c>
-      <c r="L101">
-        <v>8.585000000000001</v>
-      </c>
-      <c r="M101">
-        <v>4.2248646</v>
-      </c>
-      <c r="N101">
-        <v>4.360135400000001</v>
-      </c>
-      <c r="O101">
-        <v>1.286239943</v>
-      </c>
-      <c r="P101">
-        <v>3.073895457000001</v>
-      </c>
-      <c r="Q101">
-        <v>10.613895457</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.409429124330485</v>
-      </c>
-      <c r="T101">
-        <v>67.50395475303114</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.295</v>
-      </c>
-      <c r="W101">
-        <v>0.05343900000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.032017783481156</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
